--- a/public/data/products_master.xlsx
+++ b/public/data/products_master.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="12580"/>
+    <workbookView windowWidth="29400" windowHeight="12700"/>
   </bookViews>
   <sheets>
     <sheet name="Işıklar Ürün Listesi" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Işıklar Ürün Listesi'!$A$1:$L$658</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Işıklar Ürün Listesi'!$A$1:$L$671</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5268" uniqueCount="2510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5372" uniqueCount="2562">
   <si>
     <t>TSE</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Üretimimiz</t>
   </si>
   <si>
-    <t>Renk</t>
+    <t>Studio</t>
   </si>
   <si>
     <t>Kaynak</t>
@@ -9268,6 +9268,227 @@
   </si>
   <si>
     <t>DCK-DRZ-1.jpg</t>
+  </si>
+  <si>
+    <t>DCK-DRZ-2</t>
+  </si>
+  <si>
+    <t>DCK Geniş Derz Dolgu Harcı (Koyu Gri)</t>
+  </si>
+  <si>
+    <t>• Ürün Tipi: DCK Kaplama Tuğla Özel Flex Derz Dolgu Harcı (Koyu Gri)
+• Standart &amp; Sınıf: TS EN 13888-1 standardına uygun CG2 WA Sınıfı (Çimento esaslı, polimer takviyeli, yüksek performanslı flex derz dolgusu).
+• Uygulama Aralığı: 5 - 20 mm geniş ve derin derz aralıkları için özel formüle edilmiştir (Çatlama ve büzülme yapmaz, büzülme oranı ≤ 3 mm/m).
+• Kullanım Alanları: İç ve dış mekanlarda; pres tuğla, kaplama tuğlası, klinker tuğla, el yapımı tuğla, doğal taş, granit, seramik ve ıslak hacimlerin (havuz, su deposu, banyo) yatay/düşey derzlerinde kullanılır.
+• Dayanım Performansı: Kuru ortam ve donma-çözünme çevrimleri sonrası basınç mukavemeti ≥ 15 MPa, eğilme mukavemeti ≥ 2.5 MPa; yüksek aşınma direnci (≤ 1000 mm³) ve termal şok dayanımı.
+• Su İticilik &amp; Renk Bütünlüğü: Azaltılmış su emme özelliği (30 dk ≤ 2 gr, 240 dk ≤ 5 gr) sayesinde dış cephelerde tuz kusmasını önler ve solmayan kalıcı renk stabilitesi sağlar.</t>
+  </si>
+  <si>
+    <t>DCK-DRZ-2.jpg</t>
+  </si>
+  <si>
+    <t>DCK-DRZ-3</t>
+  </si>
+  <si>
+    <t>DCK Geniş Derz Dolgu Harcı (Antrasit)</t>
+  </si>
+  <si>
+    <t>• Ürün Tipi: DCK Kaplama Tuğla Özel Flex Derz Dolgu Harcı (Antrasit)
+• Standart &amp; Sınıf: TS EN 13888-1 standardına uygun CG2 WA Sınıfı (Çimento esaslı, polimer takviyeli, yüksek performanslı flex derz dolgusu).
+• Uygulama Aralığı: 5 - 20 mm geniş ve derin derz aralıkları için özel formüle edilmiştir (Çatlama ve büzülme yapmaz, büzülme oranı ≤ 3 mm/m).
+• Kullanım Alanları: İç ve dış mekanlarda; pres tuğla, kaplama tuğlası, klinker tuğla, el yapımı tuğla, doğal taş, granit, seramik ve ıslak hacimlerin (havuz, su deposu, banyo) yatay/düşey derzlerinde kullanılır.
+• Dayanım Performansı: Kuru ortam ve donma-çözünme çevrimleri sonrası basınç mukavemeti ≥ 15 MPa, eğilme mukavemeti ≥ 2.5 MPa; yüksek aşınma direnci (≤ 1000 mm³) ve termal şok dayanımı.
+• Su İticilik &amp; Renk Bütünlüğü: Azaltılmış su emme özelliği (30 dk ≤ 2 gr, 240 dk ≤ 5 gr) sayesinde dış cephelerde tuz kusmasını önler ve solmayan kalıcı renk stabilitesi sağlar.</t>
+  </si>
+  <si>
+    <t>DCK-DRZ-3.jpg</t>
+  </si>
+  <si>
+    <t>DCK-DRZ-4</t>
+  </si>
+  <si>
+    <t>DCK Geniş Derz Dolgu Harcı (Siyah)</t>
+  </si>
+  <si>
+    <t>• Ürün Tipi: DCK Kaplama Tuğla Özel Flex Derz Dolgu Harcı (Siyah)
+• Standart &amp; Sınıf: TS EN 13888-1 standardına uygun CG2 WA Sınıfı (Çimento esaslı, polimer takviyeli, yüksek performanslı flex derz dolgusu).
+• Uygulama Aralığı: 5 - 20 mm geniş ve derin derz aralıkları için özel formüle edilmiştir (Çatlama ve büzülme yapmaz, büzülme oranı ≤ 3 mm/m).
+• Kullanım Alanları: İç ve dış mekanlarda; pres tuğla, kaplama tuğlası, klinker tuğla, el yapımı tuğla, doğal taş, granit, seramik ve ıslak hacimlerin (havuz, su deposu, banyo) yatay/düşey derzlerinde kullanılır.
+• Dayanım Performansı: Kuru ortam ve donma-çözünme çevrimleri sonrası basınç mukavemeti ≥ 15 MPa, eğilme mukavemeti ≥ 2.5 MPa; yüksek aşınma direnci (≤ 1000 mm³) ve termal şok dayanımı.
+• Su İticilik &amp; Renk Bütünlüğü: Azaltılmış su emme özelliği (30 dk ≤ 2 gr, 240 dk ≤ 5 gr) sayesinde dış cephelerde tuz kusmasını önler ve solmayan kalıcı renk stabilitesi sağlar.</t>
+  </si>
+  <si>
+    <t>DCK-DRZ-4.jpg</t>
+  </si>
+  <si>
+    <t>DCK-DRZ-5</t>
+  </si>
+  <si>
+    <t>DCK Geniş Derz Dolgu Harcı (Beyaz)</t>
+  </si>
+  <si>
+    <t>• Ürün Tipi: DCK Kaplama Tuğla Özel Flex Derz Dolgu Harcı (Beyaz)
+• Standart &amp; Sınıf: TS EN 13888-1 standardına uygun CG2 WA Sınıfı (Çimento esaslı, polimer takviyeli, yüksek performanslı flex derz dolgusu).
+• Uygulama Aralığı: 5 - 20 mm geniş ve derin derz aralıkları için özel formüle edilmiştir (Çatlama ve büzülme yapmaz, büzülme oranı ≤ 3 mm/m).
+• Kullanım Alanları: İç ve dış mekanlarda; pres tuğla, kaplama tuğlası, klinker tuğla, el yapımı tuğla, doğal taş, granit, seramik ve ıslak hacimlerin (havuz, su deposu, banyo) yatay/düşey derzlerinde kullanılır.
+• Dayanım Performansı: Kuru ortam ve donma-çözünme çevrimleri sonrası basınç mukavemeti ≥ 15 MPa, eğilme mukavemeti ≥ 2.5 MPa; yüksek aşınma direnci (≤ 1000 mm³) ve termal şok dayanımı.
+• Su İticilik &amp; Renk Bütünlüğü: Azaltılmış su emme özelliği (30 dk ≤ 2 gr, 240 dk ≤ 5 gr) sayesinde dış cephelerde tuz kusmasını önler ve solmayan kalıcı renk stabilitesi sağlar.</t>
+  </si>
+  <si>
+    <t>DCK-DRZ-5.jpg</t>
+  </si>
+  <si>
+    <t>DCK-DRZ-6</t>
+  </si>
+  <si>
+    <t>DCK Geniş Derz Dolgu Harcı (Bej)</t>
+  </si>
+  <si>
+    <t>• Ürün Tipi: DCK Kaplama Tuğla Özel Flex Derz Dolgu Harcı (Bej)
+• Standart &amp; Sınıf: TS EN 13888-1 standardına uygun CG2 WA Sınıfı (Çimento esaslı, polimer takviyeli, yüksek performanslı flex derz dolgusu).
+• Uygulama Aralığı: 5 - 20 mm geniş ve derin derz aralıkları için özel formüle edilmiştir (Çatlama ve büzülme yapmaz, büzülme oranı ≤ 3 mm/m).
+• Kullanım Alanları: İç ve dış mekanlarda; pres tuğla, kaplama tuğlası, klinker tuğla, el yapımı tuğla, doğal taş, granit, seramik ve ıslak hacimlerin (havuz, su deposu, banyo) yatay/düşey derzlerinde kullanılır.
+• Dayanım Performansı: Kuru ortam ve donma-çözünme çevrimleri sonrası basınç mukavemeti ≥ 15 MPa, eğilme mukavemeti ≥ 2.5 MPa; yüksek aşınma direnci (≤ 1000 mm³) ve termal şok dayanımı.
+• Su İticilik &amp; Renk Bütünlüğü: Azaltılmış su emme özelliği (30 dk ≤ 2 gr, 240 dk ≤ 5 gr) sayesinde dış cephelerde tuz kusmasını önler ve solmayan kalıcı renk stabilitesi sağlar.</t>
+  </si>
+  <si>
+    <t>DCK-DRZ-6.jpg</t>
+  </si>
+  <si>
+    <t>DCK-DRZ-7</t>
+  </si>
+  <si>
+    <t>DCK Geniş Derz Dolgu Harcı (Gökmavi)</t>
+  </si>
+  <si>
+    <t>• Ürün Tipi: DCK Kaplama Tuğla Özel Flex Derz Dolgu Harcı (Gökmavi)
+• Standart &amp; Sınıf: TS EN 13888-1 standardına uygun CG2 WA Sınıfı (Çimento esaslı, polimer takviyeli, yüksek performanslı flex derz dolgusu).
+• Uygulama Aralığı: 5 - 20 mm geniş ve derin derz aralıkları için özel formüle edilmiştir (Çatlama ve büzülme yapmaz, büzülme oranı ≤ 3 mm/m).
+• Kullanım Alanları: İç ve dış mekanlarda; pres tuğla, kaplama tuğlası, klinker tuğla, el yapımı tuğla, doğal taş, granit, seramik ve ıslak hacimlerin (havuz, su deposu, banyo) yatay/düşey derzlerinde kullanılır.
+• Dayanım Performansı: Kuru ortam ve donma-çözünme çevrimleri sonrası basınç mukavemeti ≥ 15 MPa, eğilme mukavemeti ≥ 2.5 MPa; yüksek aşınma direnci (≤ 1000 mm³) ve termal şok dayanımı.
+• Su İticilik &amp; Renk Bütünlüğü: Azaltılmış su emme özelliği (30 dk ≤ 2 gr, 240 dk ≤ 5 gr) sayesinde dış cephelerde tuz kusmasını önler ve solmayan kalıcı renk stabilitesi sağlar.</t>
+  </si>
+  <si>
+    <t>DCK-DRZ-7.jpg</t>
+  </si>
+  <si>
+    <t>DCK-DRZ-8</t>
+  </si>
+  <si>
+    <t>DCK Geniş Derz Dolgu Harcı (Sütlü Kahve)</t>
+  </si>
+  <si>
+    <t>• Ürün Tipi: DCK Kaplama Tuğla Özel Flex Derz Dolgu Harcı (Sütlü Kahve)
+• Standart &amp; Sınıf: TS EN 13888-1 standardına uygun CG2 WA Sınıfı (Çimento esaslı, polimer takviyeli, yüksek performanslı flex derz dolgusu).
+• Uygulama Aralığı: 5 - 20 mm geniş ve derin derz aralıkları için özel formüle edilmiştir (Çatlama ve büzülme yapmaz, büzülme oranı ≤ 3 mm/m).
+• Kullanım Alanları: İç ve dış mekanlarda; pres tuğla, kaplama tuğlası, klinker tuğla, el yapımı tuğla, doğal taş, granit, seramik ve ıslak hacimlerin (havuz, su deposu, banyo) yatay/düşey derzlerinde kullanılır.
+• Dayanım Performansı: Kuru ortam ve donma-çözünme çevrimleri sonrası basınç mukavemeti ≥ 15 MPa, eğilme mukavemeti ≥ 2.5 MPa; yüksek aşınma direnci (≤ 1000 mm³) ve termal şok dayanımı.
+• Su İticilik &amp; Renk Bütünlüğü: Azaltılmış su emme özelliği (30 dk ≤ 2 gr, 240 dk ≤ 5 gr) sayesinde dış cephelerde tuz kusmasını önler ve solmayan kalıcı renk stabilitesi sağlar.</t>
+  </si>
+  <si>
+    <t>DCK-DRZ-8.jpg</t>
+  </si>
+  <si>
+    <t>DCK-DRZ-9</t>
+  </si>
+  <si>
+    <t>DCK Geniş Derz Dolgu Harcı (Kahve)</t>
+  </si>
+  <si>
+    <t>• Ürün Tipi: DCK Kaplama Tuğla Özel Flex Derz Dolgu Harcı (Kahve)
+• Standart &amp; Sınıf: TS EN 13888-1 standardına uygun CG2 WA Sınıfı (Çimento esaslı, polimer takviyeli, yüksek performanslı flex derz dolgusu).
+• Uygulama Aralığı: 5 - 20 mm geniş ve derin derz aralıkları için özel formüle edilmiştir (Çatlama ve büzülme yapmaz, büzülme oranı ≤ 3 mm/m).
+• Kullanım Alanları: İç ve dış mekanlarda; pres tuğla, kaplama tuğlası, klinker tuğla, el yapımı tuğla, doğal taş, granit, seramik ve ıslak hacimlerin (havuz, su deposu, banyo) yatay/düşey derzlerinde kullanılır.
+• Dayanım Performansı: Kuru ortam ve donma-çözünme çevrimleri sonrası basınç mukavemeti ≥ 15 MPa, eğilme mukavemeti ≥ 2.5 MPa; yüksek aşınma direnci (≤ 1000 mm³) ve termal şok dayanımı.
+• Su İticilik &amp; Renk Bütünlüğü: Azaltılmış su emme özelliği (30 dk ≤ 2 gr, 240 dk ≤ 5 gr) sayesinde dış cephelerde tuz kusmasını önler ve solmayan kalıcı renk stabilitesi sağlar.</t>
+  </si>
+  <si>
+    <t>DCK-DRZ-9.jpg</t>
+  </si>
+  <si>
+    <t>DCK-DRZ-10</t>
+  </si>
+  <si>
+    <t>DCK Geniş Derz Dolgu Harcı (Eflatun)</t>
+  </si>
+  <si>
+    <t>• Ürün Tipi: DCK Kaplama Tuğla Özel Flex Derz Dolgu Harcı (Eflatun)
+• Standart &amp; Sınıf: TS EN 13888-1 standardına uygun CG2 WA Sınıfı (Çimento esaslı, polimer takviyeli, yüksek performanslı flex derz dolgusu).
+• Uygulama Aralığı: 5 - 20 mm geniş ve derin derz aralıkları için özel formüle edilmiştir (Çatlama ve büzülme yapmaz, büzülme oranı ≤ 3 mm/m).
+• Kullanım Alanları: İç ve dış mekanlarda; pres tuğla, kaplama tuğlası, klinker tuğla, el yapımı tuğla, doğal taş, granit, seramik ve ıslak hacimlerin (havuz, su deposu, banyo) yatay/düşey derzlerinde kullanılır.
+• Dayanım Performansı: Kuru ortam ve donma-çözünme çevrimleri sonrası basınç mukavemeti ≥ 15 MPa, eğilme mukavemeti ≥ 2.5 MPa; yüksek aşınma direnci (≤ 1000 mm³) ve termal şok dayanımı.
+• Su İticilik &amp; Renk Bütünlüğü: Azaltılmış su emme özelliği (30 dk ≤ 2 gr, 240 dk ≤ 5 gr) sayesinde dış cephelerde tuz kusmasını önler ve solmayan kalıcı renk stabilitesi sağlar.</t>
+  </si>
+  <si>
+    <t>DCK-DRZ-10.jpg</t>
+  </si>
+  <si>
+    <t>DCK-DRZ-11</t>
+  </si>
+  <si>
+    <t>DCK Geniş Derz Dolgu Harcı (Krem)</t>
+  </si>
+  <si>
+    <t>• Ürün Tipi: DCK Kaplama Tuğla Özel Flex Derz Dolgu Harcı (Krem)
+• Standart &amp; Sınıf: TS EN 13888-1 standardına uygun CG2 WA Sınıfı (Çimento esaslı, polimer takviyeli, yüksek performanslı flex derz dolgusu).
+• Uygulama Aralığı: 5 - 20 mm geniş ve derin derz aralıkları için özel formüle edilmiştir (Çatlama ve büzülme yapmaz, büzülme oranı ≤ 3 mm/m).
+• Kullanım Alanları: İç ve dış mekanlarda; pres tuğla, kaplama tuğlası, klinker tuğla, el yapımı tuğla, doğal taş, granit, seramik ve ıslak hacimlerin (havuz, su deposu, banyo) yatay/düşey derzlerinde kullanılır.
+• Dayanım Performansı: Kuru ortam ve donma-çözünme çevrimleri sonrası basınç mukavemeti ≥ 15 MPa, eğilme mukavemeti ≥ 2.5 MPa; yüksek aşınma direnci (≤ 1000 mm³) ve termal şok dayanımı.
+• Su İticilik &amp; Renk Bütünlüğü: Azaltılmış su emme özelliği (30 dk ≤ 2 gr, 240 dk ≤ 5 gr) sayesinde dış cephelerde tuz kusmasını önler ve solmayan kalıcı renk stabilitesi sağlar.</t>
+  </si>
+  <si>
+    <t>DCK-DRZ-11.jpg</t>
+  </si>
+  <si>
+    <t>DCK-DRZ-12</t>
+  </si>
+  <si>
+    <t>DCK Geniş Derz Dolgu Harcı (Gül Kurusu)</t>
+  </si>
+  <si>
+    <t>• Ürün Tipi: DCK Kaplama Tuğla Özel Flex Derz Dolgu Harcı (Gül Kurusu)
+• Standart &amp; Sınıf: TS EN 13888-1 standardına uygun CG2 WA Sınıfı (Çimento esaslı, polimer takviyeli, yüksek performanslı flex derz dolgusu).
+• Uygulama Aralığı: 5 - 20 mm geniş ve derin derz aralıkları için özel formüle edilmiştir (Çatlama ve büzülme yapmaz, büzülme oranı ≤ 3 mm/m).
+• Kullanım Alanları: İç ve dış mekanlarda; pres tuğla, kaplama tuğlası, klinker tuğla, el yapımı tuğla, doğal taş, granit, seramik ve ıslak hacimlerin (havuz, su deposu, banyo) yatay/düşey derzlerinde kullanılır.
+• Dayanım Performansı: Kuru ortam ve donma-çözünme çevrimleri sonrası basınç mukavemeti ≥ 15 MPa, eğilme mukavemeti ≥ 2.5 MPa; yüksek aşınma direnci (≤ 1000 mm³) ve termal şok dayanımı.
+• Su İticilik &amp; Renk Bütünlüğü: Azaltılmış su emme özelliği (30 dk ≤ 2 gr, 240 dk ≤ 5 gr) sayesinde dış cephelerde tuz kusmasını önler ve solmayan kalıcı renk stabilitesi sağlar.</t>
+  </si>
+  <si>
+    <t>DCK-DRZ-12.jpg</t>
+  </si>
+  <si>
+    <t>DCK-DRZ-13</t>
+  </si>
+  <si>
+    <t>DCK Geniş Derz Dolgu Harcı (Şampanya)</t>
+  </si>
+  <si>
+    <t>• Ürün Tipi: DCK Kaplama Tuğla Özel Flex Derz Dolgu Harcı (Şampanya)
+• Standart &amp; Sınıf: TS EN 13888-1 standardına uygun CG2 WA Sınıfı (Çimento esaslı, polimer takviyeli, yüksek performanslı flex derz dolgusu).
+• Uygulama Aralığı: 5 - 20 mm geniş ve derin derz aralıkları için özel formüle edilmiştir (Çatlama ve büzülme yapmaz, büzülme oranı ≤ 3 mm/m).
+• Kullanım Alanları: İç ve dış mekanlarda; pres tuğla, kaplama tuğlası, klinker tuğla, el yapımı tuğla, doğal taş, granit, seramik ve ıslak hacimlerin (havuz, su deposu, banyo) yatay/düşey derzlerinde kullanılır.
+• Dayanım Performansı: Kuru ortam ve donma-çözünme çevrimleri sonrası basınç mukavemeti ≥ 15 MPa, eğilme mukavemeti ≥ 2.5 MPa; yüksek aşınma direnci (≤ 1000 mm³) ve termal şok dayanımı.
+• Su İticilik &amp; Renk Bütünlüğü: Azaltılmış su emme özelliği (30 dk ≤ 2 gr, 240 dk ≤ 5 gr) sayesinde dış cephelerde tuz kusmasını önler ve solmayan kalıcı renk stabilitesi sağlar.</t>
+  </si>
+  <si>
+    <t>DCK-DRZ-13.jpg</t>
+  </si>
+  <si>
+    <t>DCK-DRZ-14</t>
+  </si>
+  <si>
+    <t>DCK Geniş Derz Dolgu Harcı (Buz Mavisi)</t>
+  </si>
+  <si>
+    <t>• Ürün Tipi: DCK Kaplama Tuğla Özel Flex Derz Dolgu Harcı (Buz Mavisi)
+• Standart &amp; Sınıf: TS EN 13888-1 standardına uygun CG2 WA Sınıfı (Çimento esaslı, polimer takviyeli, yüksek performanslı flex derz dolgusu).
+• Uygulama Aralığı: 5 - 20 mm geniş ve derin derz aralıkları için özel formüle edilmiştir (Çatlama ve büzülme yapmaz, büzülme oranı ≤ 3 mm/m).
+• Kullanım Alanları: İç ve dış mekanlarda; pres tuğla, kaplama tuğlası, klinker tuğla, el yapımı tuğla, doğal taş, granit, seramik ve ıslak hacimlerin (havuz, su deposu, banyo) yatay/düşey derzlerinde kullanılır.
+• Dayanım Performansı: Kuru ortam ve donma-çözünme çevrimleri sonrası basınç mukavemeti ≥ 15 MPa, eğilme mukavemeti ≥ 2.5 MPa; yüksek aşınma direnci (≤ 1000 mm³) ve termal şok dayanımı.
+• Su İticilik &amp; Renk Bütünlüğü: Azaltılmış su emme özelliği (30 dk ≤ 2 gr, 240 dk ≤ 5 gr) sayesinde dış cephelerde tuz kusmasını önler ve solmayan kalıcı renk stabilitesi sağlar.</t>
+  </si>
+  <si>
+    <t>DCK-DRZ-14.jpg</t>
   </si>
   <si>
     <t>DCK-FYN-1</t>
@@ -10402,8 +10623,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L658"/>
+  <dimension ref="A1:L671"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <cols>
+    <col min="2" max="3" width="9.75" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" t="s">
@@ -10444,6 +10668,9 @@
       </c>
     </row>
     <row r="2" spans="1:12">
+      <c r="C2">
+        <v>1</v>
+      </c>
       <c r="D2" t="s">
         <v>12</v>
       </c>
@@ -10470,6 +10697,9 @@
       </c>
     </row>
     <row r="3" spans="1:12">
+      <c r="C3">
+        <v>1</v>
+      </c>
       <c r="D3" t="s">
         <v>12</v>
       </c>
@@ -10496,6 +10726,9 @@
       </c>
     </row>
     <row r="4" spans="1:12">
+      <c r="C4">
+        <v>1</v>
+      </c>
       <c r="D4" t="s">
         <v>12</v>
       </c>
@@ -10522,6 +10755,9 @@
       </c>
     </row>
     <row r="5" spans="1:12">
+      <c r="C5">
+        <v>1</v>
+      </c>
       <c r="D5" t="s">
         <v>12</v>
       </c>
@@ -10548,6 +10784,9 @@
       </c>
     </row>
     <row r="6" spans="1:12">
+      <c r="C6">
+        <v>1</v>
+      </c>
       <c r="D6" t="s">
         <v>12</v>
       </c>
@@ -10574,6 +10813,9 @@
       </c>
     </row>
     <row r="7" spans="1:12">
+      <c r="C7">
+        <v>1</v>
+      </c>
       <c r="D7" t="s">
         <v>12</v>
       </c>
@@ -10600,6 +10842,9 @@
       </c>
     </row>
     <row r="8" spans="1:12">
+      <c r="C8">
+        <v>1</v>
+      </c>
       <c r="D8" t="s">
         <v>12</v>
       </c>
@@ -10626,6 +10871,9 @@
       </c>
     </row>
     <row r="9" spans="1:12">
+      <c r="C9">
+        <v>1</v>
+      </c>
       <c r="D9" t="s">
         <v>12</v>
       </c>
@@ -10652,6 +10900,9 @@
       </c>
     </row>
     <row r="10" spans="1:12">
+      <c r="C10">
+        <v>1</v>
+      </c>
       <c r="D10" t="s">
         <v>12</v>
       </c>
@@ -10678,6 +10929,9 @@
       </c>
     </row>
     <row r="11" spans="1:12">
+      <c r="C11">
+        <v>1</v>
+      </c>
       <c r="D11" t="s">
         <v>12</v>
       </c>
@@ -10704,6 +10958,9 @@
       </c>
     </row>
     <row r="12" spans="1:12">
+      <c r="C12">
+        <v>1</v>
+      </c>
       <c r="D12" t="s">
         <v>12</v>
       </c>
@@ -10730,6 +10987,9 @@
       </c>
     </row>
     <row r="13" spans="1:12">
+      <c r="C13">
+        <v>1</v>
+      </c>
       <c r="D13" t="s">
         <v>12</v>
       </c>
@@ -10756,6 +11016,9 @@
       </c>
     </row>
     <row r="14" spans="1:12">
+      <c r="C14">
+        <v>1</v>
+      </c>
       <c r="D14" t="s">
         <v>12</v>
       </c>
@@ -10782,6 +11045,9 @@
       </c>
     </row>
     <row r="15" spans="1:12">
+      <c r="C15">
+        <v>1</v>
+      </c>
       <c r="D15" t="s">
         <v>12</v>
       </c>
@@ -10808,6 +11074,9 @@
       </c>
     </row>
     <row r="16" spans="1:12">
+      <c r="C16">
+        <v>1</v>
+      </c>
       <c r="D16" t="s">
         <v>12</v>
       </c>
@@ -10833,7 +11102,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="17" spans="4:11">
+    <row r="17" spans="3:11">
+      <c r="C17">
+        <v>1</v>
+      </c>
       <c r="D17" t="s">
         <v>12</v>
       </c>
@@ -10859,7 +11131,10 @@
         <v>79</v>
       </c>
     </row>
-    <row r="18" spans="4:11">
+    <row r="18" spans="3:11">
+      <c r="C18">
+        <v>1</v>
+      </c>
       <c r="D18" t="s">
         <v>12</v>
       </c>
@@ -10885,7 +11160,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="19" spans="4:11">
+    <row r="19" spans="3:11">
+      <c r="C19">
+        <v>1</v>
+      </c>
       <c r="D19" t="s">
         <v>12</v>
       </c>
@@ -10911,7 +11189,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="20" spans="4:11">
+    <row r="20" spans="3:11">
+      <c r="C20">
+        <v>1</v>
+      </c>
       <c r="D20" t="s">
         <v>12</v>
       </c>
@@ -10937,7 +11218,10 @@
         <v>91</v>
       </c>
     </row>
-    <row r="21" spans="4:11">
+    <row r="21" spans="3:11">
+      <c r="C21">
+        <v>1</v>
+      </c>
       <c r="D21" t="s">
         <v>12</v>
       </c>
@@ -10963,7 +11247,10 @@
         <v>95</v>
       </c>
     </row>
-    <row r="22" spans="4:11">
+    <row r="22" spans="3:11">
+      <c r="C22">
+        <v>1</v>
+      </c>
       <c r="D22" t="s">
         <v>12</v>
       </c>
@@ -10989,7 +11276,10 @@
         <v>99</v>
       </c>
     </row>
-    <row r="23" spans="4:11">
+    <row r="23" spans="3:11">
+      <c r="C23">
+        <v>1</v>
+      </c>
       <c r="D23" t="s">
         <v>12</v>
       </c>
@@ -11015,7 +11305,10 @@
         <v>103</v>
       </c>
     </row>
-    <row r="24" spans="4:11">
+    <row r="24" spans="3:11">
+      <c r="C24">
+        <v>1</v>
+      </c>
       <c r="D24" t="s">
         <v>12</v>
       </c>
@@ -11041,7 +11334,10 @@
         <v>107</v>
       </c>
     </row>
-    <row r="25" spans="4:11">
+    <row r="25" spans="3:11">
+      <c r="C25">
+        <v>1</v>
+      </c>
       <c r="D25" t="s">
         <v>12</v>
       </c>
@@ -11067,7 +11363,10 @@
         <v>113</v>
       </c>
     </row>
-    <row r="26" spans="4:11">
+    <row r="26" spans="3:11">
+      <c r="C26">
+        <v>1</v>
+      </c>
       <c r="D26" t="s">
         <v>12</v>
       </c>
@@ -11093,7 +11392,10 @@
         <v>117</v>
       </c>
     </row>
-    <row r="27" spans="4:11">
+    <row r="27" spans="3:11">
+      <c r="C27">
+        <v>1</v>
+      </c>
       <c r="D27" t="s">
         <v>12</v>
       </c>
@@ -11119,7 +11421,10 @@
         <v>121</v>
       </c>
     </row>
-    <row r="28" spans="4:11">
+    <row r="28" spans="3:11">
+      <c r="C28">
+        <v>1</v>
+      </c>
       <c r="D28" t="s">
         <v>12</v>
       </c>
@@ -11145,7 +11450,10 @@
         <v>125</v>
       </c>
     </row>
-    <row r="29" spans="4:11">
+    <row r="29" spans="3:11">
+      <c r="C29">
+        <v>1</v>
+      </c>
       <c r="D29" t="s">
         <v>12</v>
       </c>
@@ -11171,7 +11479,10 @@
         <v>129</v>
       </c>
     </row>
-    <row r="30" spans="4:11">
+    <row r="30" spans="3:11">
+      <c r="C30">
+        <v>1</v>
+      </c>
       <c r="D30" t="s">
         <v>12</v>
       </c>
@@ -11197,7 +11508,10 @@
         <v>133</v>
       </c>
     </row>
-    <row r="31" spans="4:11">
+    <row r="31" spans="3:11">
+      <c r="C31">
+        <v>1</v>
+      </c>
       <c r="D31" t="s">
         <v>12</v>
       </c>
@@ -11223,7 +11537,10 @@
         <v>137</v>
       </c>
     </row>
-    <row r="32" spans="4:11">
+    <row r="32" spans="3:11">
+      <c r="C32">
+        <v>1</v>
+      </c>
       <c r="D32" t="s">
         <v>12</v>
       </c>
@@ -11249,7 +11566,10 @@
         <v>141</v>
       </c>
     </row>
-    <row r="33" spans="4:11">
+    <row r="33" spans="3:11">
+      <c r="C33">
+        <v>1</v>
+      </c>
       <c r="D33" t="s">
         <v>12</v>
       </c>
@@ -11275,7 +11595,10 @@
         <v>145</v>
       </c>
     </row>
-    <row r="34" spans="4:11">
+    <row r="34" spans="3:11">
+      <c r="C34">
+        <v>1</v>
+      </c>
       <c r="D34" t="s">
         <v>12</v>
       </c>
@@ -11301,7 +11624,10 @@
         <v>149</v>
       </c>
     </row>
-    <row r="35" spans="4:11">
+    <row r="35" spans="3:11">
+      <c r="C35">
+        <v>1</v>
+      </c>
       <c r="D35" t="s">
         <v>12</v>
       </c>
@@ -11327,7 +11653,10 @@
         <v>153</v>
       </c>
     </row>
-    <row r="36" spans="4:11">
+    <row r="36" spans="3:11">
+      <c r="C36">
+        <v>1</v>
+      </c>
       <c r="D36" t="s">
         <v>12</v>
       </c>
@@ -11353,7 +11682,10 @@
         <v>157</v>
       </c>
     </row>
-    <row r="37" spans="4:11">
+    <row r="37" spans="3:11">
+      <c r="C37">
+        <v>1</v>
+      </c>
       <c r="D37" t="s">
         <v>12</v>
       </c>
@@ -11379,7 +11711,10 @@
         <v>161</v>
       </c>
     </row>
-    <row r="38" spans="4:11">
+    <row r="38" spans="3:11">
+      <c r="C38">
+        <v>1</v>
+      </c>
       <c r="D38" t="s">
         <v>12</v>
       </c>
@@ -11405,7 +11740,10 @@
         <v>165</v>
       </c>
     </row>
-    <row r="39" spans="4:11">
+    <row r="39" spans="3:11">
+      <c r="C39">
+        <v>1</v>
+      </c>
       <c r="D39" t="s">
         <v>12</v>
       </c>
@@ -11431,7 +11769,10 @@
         <v>169</v>
       </c>
     </row>
-    <row r="40" spans="4:11">
+    <row r="40" spans="3:11">
+      <c r="C40">
+        <v>1</v>
+      </c>
       <c r="D40" t="s">
         <v>12</v>
       </c>
@@ -11457,7 +11798,10 @@
         <v>173</v>
       </c>
     </row>
-    <row r="41" spans="4:11">
+    <row r="41" spans="3:11">
+      <c r="C41">
+        <v>1</v>
+      </c>
       <c r="D41" t="s">
         <v>12</v>
       </c>
@@ -11483,7 +11827,10 @@
         <v>177</v>
       </c>
     </row>
-    <row r="42" spans="4:11">
+    <row r="42" spans="3:11">
+      <c r="C42">
+        <v>1</v>
+      </c>
       <c r="D42" t="s">
         <v>12</v>
       </c>
@@ -11509,7 +11856,10 @@
         <v>181</v>
       </c>
     </row>
-    <row r="43" spans="4:11">
+    <row r="43" spans="3:11">
+      <c r="C43">
+        <v>1</v>
+      </c>
       <c r="D43" t="s">
         <v>12</v>
       </c>
@@ -11535,7 +11885,10 @@
         <v>185</v>
       </c>
     </row>
-    <row r="44" spans="4:11">
+    <row r="44" spans="3:11">
+      <c r="C44">
+        <v>1</v>
+      </c>
       <c r="D44" t="s">
         <v>12</v>
       </c>
@@ -11561,7 +11914,10 @@
         <v>189</v>
       </c>
     </row>
-    <row r="45" spans="4:11">
+    <row r="45" spans="3:11">
+      <c r="C45">
+        <v>1</v>
+      </c>
       <c r="D45" t="s">
         <v>12</v>
       </c>
@@ -11587,7 +11943,10 @@
         <v>193</v>
       </c>
     </row>
-    <row r="46" spans="4:11">
+    <row r="46" spans="3:11">
+      <c r="C46">
+        <v>1</v>
+      </c>
       <c r="D46" t="s">
         <v>12</v>
       </c>
@@ -11613,7 +11972,10 @@
         <v>197</v>
       </c>
     </row>
-    <row r="47" spans="4:11">
+    <row r="47" spans="3:11">
+      <c r="C47">
+        <v>1</v>
+      </c>
       <c r="D47" t="s">
         <v>12</v>
       </c>
@@ -11639,7 +12001,10 @@
         <v>201</v>
       </c>
     </row>
-    <row r="48" spans="4:11">
+    <row r="48" spans="3:11">
+      <c r="C48">
+        <v>1</v>
+      </c>
       <c r="D48" t="s">
         <v>12</v>
       </c>
@@ -11665,7 +12030,10 @@
         <v>205</v>
       </c>
     </row>
-    <row r="49" spans="4:11">
+    <row r="49" spans="3:11">
+      <c r="C49">
+        <v>1</v>
+      </c>
       <c r="D49" t="s">
         <v>12</v>
       </c>
@@ -11691,7 +12059,10 @@
         <v>209</v>
       </c>
     </row>
-    <row r="50" spans="4:11">
+    <row r="50" spans="3:11">
+      <c r="C50">
+        <v>1</v>
+      </c>
       <c r="D50" t="s">
         <v>12</v>
       </c>
@@ -11717,7 +12088,10 @@
         <v>213</v>
       </c>
     </row>
-    <row r="51" spans="4:11">
+    <row r="51" spans="3:11">
+      <c r="C51">
+        <v>1</v>
+      </c>
       <c r="D51" t="s">
         <v>12</v>
       </c>
@@ -11743,7 +12117,10 @@
         <v>217</v>
       </c>
     </row>
-    <row r="52" spans="4:11">
+    <row r="52" spans="3:11">
+      <c r="C52">
+        <v>1</v>
+      </c>
       <c r="D52" t="s">
         <v>12</v>
       </c>
@@ -11769,7 +12146,10 @@
         <v>221</v>
       </c>
     </row>
-    <row r="53" spans="4:11">
+    <row r="53" spans="3:11">
+      <c r="C53">
+        <v>1</v>
+      </c>
       <c r="D53" t="s">
         <v>12</v>
       </c>
@@ -11795,7 +12175,10 @@
         <v>225</v>
       </c>
     </row>
-    <row r="54" spans="4:11">
+    <row r="54" spans="3:11">
+      <c r="C54">
+        <v>1</v>
+      </c>
       <c r="D54" t="s">
         <v>12</v>
       </c>
@@ -11821,7 +12204,10 @@
         <v>229</v>
       </c>
     </row>
-    <row r="55" spans="4:11">
+    <row r="55" spans="3:11">
+      <c r="C55">
+        <v>1</v>
+      </c>
       <c r="D55" t="s">
         <v>12</v>
       </c>
@@ -11847,7 +12233,10 @@
         <v>233</v>
       </c>
     </row>
-    <row r="56" spans="4:11">
+    <row r="56" spans="3:11">
+      <c r="C56">
+        <v>1</v>
+      </c>
       <c r="D56" t="s">
         <v>12</v>
       </c>
@@ -11873,7 +12262,10 @@
         <v>237</v>
       </c>
     </row>
-    <row r="57" spans="4:11">
+    <row r="57" spans="3:11">
+      <c r="C57">
+        <v>1</v>
+      </c>
       <c r="D57" t="s">
         <v>12</v>
       </c>
@@ -11899,7 +12291,10 @@
         <v>241</v>
       </c>
     </row>
-    <row r="58" spans="4:11">
+    <row r="58" spans="3:11">
+      <c r="C58">
+        <v>1</v>
+      </c>
       <c r="D58" t="s">
         <v>12</v>
       </c>
@@ -11925,7 +12320,10 @@
         <v>245</v>
       </c>
     </row>
-    <row r="59" spans="4:11">
+    <row r="59" spans="3:11">
+      <c r="C59">
+        <v>1</v>
+      </c>
       <c r="D59" t="s">
         <v>12</v>
       </c>
@@ -11951,7 +12349,10 @@
         <v>249</v>
       </c>
     </row>
-    <row r="60" spans="4:11">
+    <row r="60" spans="3:11">
+      <c r="C60">
+        <v>1</v>
+      </c>
       <c r="D60" t="s">
         <v>12</v>
       </c>
@@ -11977,7 +12378,10 @@
         <v>253</v>
       </c>
     </row>
-    <row r="61" spans="4:11">
+    <row r="61" spans="3:11">
+      <c r="C61">
+        <v>1</v>
+      </c>
       <c r="D61" t="s">
         <v>12</v>
       </c>
@@ -12003,7 +12407,10 @@
         <v>257</v>
       </c>
     </row>
-    <row r="62" spans="4:11">
+    <row r="62" spans="3:11">
+      <c r="C62">
+        <v>1</v>
+      </c>
       <c r="D62" t="s">
         <v>12</v>
       </c>
@@ -12029,7 +12436,10 @@
         <v>261</v>
       </c>
     </row>
-    <row r="63" spans="4:11">
+    <row r="63" spans="3:11">
+      <c r="C63">
+        <v>1</v>
+      </c>
       <c r="D63" t="s">
         <v>12</v>
       </c>
@@ -12055,7 +12465,10 @@
         <v>265</v>
       </c>
     </row>
-    <row r="64" spans="4:11">
+    <row r="64" spans="3:11">
+      <c r="C64">
+        <v>1</v>
+      </c>
       <c r="D64" t="s">
         <v>12</v>
       </c>
@@ -12081,7 +12494,10 @@
         <v>269</v>
       </c>
     </row>
-    <row r="65" spans="4:11">
+    <row r="65" spans="3:11">
+      <c r="C65">
+        <v>1</v>
+      </c>
       <c r="D65" t="s">
         <v>12</v>
       </c>
@@ -12107,7 +12523,10 @@
         <v>273</v>
       </c>
     </row>
-    <row r="66" spans="4:11">
+    <row r="66" spans="3:11">
+      <c r="C66">
+        <v>1</v>
+      </c>
       <c r="D66" t="s">
         <v>12</v>
       </c>
@@ -12133,7 +12552,10 @@
         <v>277</v>
       </c>
     </row>
-    <row r="67" spans="4:11">
+    <row r="67" spans="3:11">
+      <c r="C67">
+        <v>1</v>
+      </c>
       <c r="D67" t="s">
         <v>12</v>
       </c>
@@ -12159,7 +12581,10 @@
         <v>281</v>
       </c>
     </row>
-    <row r="68" spans="4:11">
+    <row r="68" spans="3:11">
+      <c r="C68">
+        <v>1</v>
+      </c>
       <c r="D68" t="s">
         <v>12</v>
       </c>
@@ -12185,7 +12610,10 @@
         <v>285</v>
       </c>
     </row>
-    <row r="69" spans="4:11">
+    <row r="69" spans="3:11">
+      <c r="C69">
+        <v>1</v>
+      </c>
       <c r="D69" t="s">
         <v>12</v>
       </c>
@@ -12211,7 +12639,10 @@
         <v>289</v>
       </c>
     </row>
-    <row r="70" spans="4:11">
+    <row r="70" spans="3:11">
+      <c r="C70">
+        <v>1</v>
+      </c>
       <c r="D70" t="s">
         <v>12</v>
       </c>
@@ -12237,7 +12668,10 @@
         <v>293</v>
       </c>
     </row>
-    <row r="71" spans="4:11">
+    <row r="71" spans="3:11">
+      <c r="C71">
+        <v>1</v>
+      </c>
       <c r="D71" t="s">
         <v>12</v>
       </c>
@@ -12263,7 +12697,10 @@
         <v>297</v>
       </c>
     </row>
-    <row r="72" spans="4:11">
+    <row r="72" spans="3:11">
+      <c r="C72">
+        <v>1</v>
+      </c>
       <c r="D72" t="s">
         <v>12</v>
       </c>
@@ -12289,7 +12726,10 @@
         <v>301</v>
       </c>
     </row>
-    <row r="73" spans="4:11">
+    <row r="73" spans="3:11">
+      <c r="C73">
+        <v>1</v>
+      </c>
       <c r="D73" t="s">
         <v>12</v>
       </c>
@@ -12315,7 +12755,10 @@
         <v>305</v>
       </c>
     </row>
-    <row r="74" spans="4:11">
+    <row r="74" spans="3:11">
+      <c r="C74">
+        <v>1</v>
+      </c>
       <c r="D74" t="s">
         <v>12</v>
       </c>
@@ -12341,7 +12784,10 @@
         <v>308</v>
       </c>
     </row>
-    <row r="75" spans="4:11">
+    <row r="75" spans="3:11">
+      <c r="C75">
+        <v>1</v>
+      </c>
       <c r="D75" t="s">
         <v>12</v>
       </c>
@@ -12367,7 +12813,10 @@
         <v>311</v>
       </c>
     </row>
-    <row r="76" spans="4:11">
+    <row r="76" spans="3:11">
+      <c r="C76">
+        <v>1</v>
+      </c>
       <c r="D76" t="s">
         <v>12</v>
       </c>
@@ -12393,7 +12842,10 @@
         <v>314</v>
       </c>
     </row>
-    <row r="77" spans="4:11">
+    <row r="77" spans="3:11">
+      <c r="C77">
+        <v>1</v>
+      </c>
       <c r="D77" t="s">
         <v>12</v>
       </c>
@@ -12419,7 +12871,10 @@
         <v>317</v>
       </c>
     </row>
-    <row r="78" spans="4:11">
+    <row r="78" spans="3:11">
+      <c r="C78">
+        <v>1</v>
+      </c>
       <c r="D78" t="s">
         <v>12</v>
       </c>
@@ -12445,7 +12900,10 @@
         <v>320</v>
       </c>
     </row>
-    <row r="79" spans="4:11">
+    <row r="79" spans="3:11">
+      <c r="C79">
+        <v>1</v>
+      </c>
       <c r="D79" t="s">
         <v>12</v>
       </c>
@@ -12471,7 +12929,10 @@
         <v>323</v>
       </c>
     </row>
-    <row r="80" spans="4:11">
+    <row r="80" spans="3:11">
+      <c r="C80">
+        <v>1</v>
+      </c>
       <c r="D80" t="s">
         <v>12</v>
       </c>
@@ -12497,7 +12958,10 @@
         <v>327</v>
       </c>
     </row>
-    <row r="81" spans="4:11">
+    <row r="81" spans="3:11">
+      <c r="C81">
+        <v>1</v>
+      </c>
       <c r="D81" t="s">
         <v>12</v>
       </c>
@@ -12523,7 +12987,10 @@
         <v>331</v>
       </c>
     </row>
-    <row r="82" spans="4:11">
+    <row r="82" spans="3:11">
+      <c r="C82">
+        <v>1</v>
+      </c>
       <c r="D82" t="s">
         <v>12</v>
       </c>
@@ -12549,7 +13016,10 @@
         <v>334</v>
       </c>
     </row>
-    <row r="83" spans="4:11">
+    <row r="83" spans="3:11">
+      <c r="C83">
+        <v>1</v>
+      </c>
       <c r="D83" t="s">
         <v>12</v>
       </c>
@@ -12575,7 +13045,10 @@
         <v>338</v>
       </c>
     </row>
-    <row r="84" spans="4:11">
+    <row r="84" spans="3:11">
+      <c r="C84">
+        <v>1</v>
+      </c>
       <c r="D84" t="s">
         <v>12</v>
       </c>
@@ -12601,7 +13074,10 @@
         <v>342</v>
       </c>
     </row>
-    <row r="85" spans="4:11">
+    <row r="85" spans="3:11">
+      <c r="C85">
+        <v>1</v>
+      </c>
       <c r="D85" t="s">
         <v>12</v>
       </c>
@@ -12627,7 +13103,10 @@
         <v>346</v>
       </c>
     </row>
-    <row r="86" spans="4:11">
+    <row r="86" spans="3:11">
+      <c r="C86">
+        <v>1</v>
+      </c>
       <c r="D86" t="s">
         <v>12</v>
       </c>
@@ -12653,7 +13132,10 @@
         <v>350</v>
       </c>
     </row>
-    <row r="87" spans="4:11">
+    <row r="87" spans="3:11">
+      <c r="C87">
+        <v>1</v>
+      </c>
       <c r="D87" t="s">
         <v>12</v>
       </c>
@@ -12679,7 +13161,10 @@
         <v>354</v>
       </c>
     </row>
-    <row r="88" spans="4:11">
+    <row r="88" spans="3:11">
+      <c r="C88">
+        <v>1</v>
+      </c>
       <c r="D88" t="s">
         <v>12</v>
       </c>
@@ -12705,7 +13190,10 @@
         <v>358</v>
       </c>
     </row>
-    <row r="89" spans="4:11">
+    <row r="89" spans="3:11">
+      <c r="C89">
+        <v>1</v>
+      </c>
       <c r="D89" t="s">
         <v>12</v>
       </c>
@@ -12731,7 +13219,10 @@
         <v>362</v>
       </c>
     </row>
-    <row r="90" spans="4:11">
+    <row r="90" spans="3:11">
+      <c r="C90">
+        <v>1</v>
+      </c>
       <c r="D90" t="s">
         <v>12</v>
       </c>
@@ -12757,7 +13248,10 @@
         <v>366</v>
       </c>
     </row>
-    <row r="91" spans="4:11">
+    <row r="91" spans="3:11">
+      <c r="C91">
+        <v>1</v>
+      </c>
       <c r="D91" t="s">
         <v>12</v>
       </c>
@@ -12783,7 +13277,10 @@
         <v>370</v>
       </c>
     </row>
-    <row r="92" spans="4:11">
+    <row r="92" spans="3:11">
+      <c r="C92">
+        <v>1</v>
+      </c>
       <c r="D92" t="s">
         <v>12</v>
       </c>
@@ -12809,7 +13306,10 @@
         <v>374</v>
       </c>
     </row>
-    <row r="93" spans="4:11">
+    <row r="93" spans="3:11">
+      <c r="C93">
+        <v>1</v>
+      </c>
       <c r="D93" t="s">
         <v>12</v>
       </c>
@@ -12835,7 +13335,10 @@
         <v>378</v>
       </c>
     </row>
-    <row r="94" spans="4:11">
+    <row r="94" spans="3:11">
+      <c r="C94">
+        <v>1</v>
+      </c>
       <c r="D94" t="s">
         <v>12</v>
       </c>
@@ -12861,7 +13364,10 @@
         <v>382</v>
       </c>
     </row>
-    <row r="95" spans="4:11">
+    <row r="95" spans="3:11">
+      <c r="C95">
+        <v>1</v>
+      </c>
       <c r="D95" t="s">
         <v>12</v>
       </c>
@@ -12887,7 +13393,10 @@
         <v>386</v>
       </c>
     </row>
-    <row r="96" spans="4:11">
+    <row r="96" spans="3:11">
+      <c r="C96">
+        <v>1</v>
+      </c>
       <c r="D96" t="s">
         <v>12</v>
       </c>
@@ -12913,7 +13422,10 @@
         <v>390</v>
       </c>
     </row>
-    <row r="97" spans="4:11">
+    <row r="97" spans="3:11">
+      <c r="C97">
+        <v>1</v>
+      </c>
       <c r="D97" t="s">
         <v>12</v>
       </c>
@@ -12939,7 +13451,10 @@
         <v>394</v>
       </c>
     </row>
-    <row r="98" spans="4:11">
+    <row r="98" spans="3:11">
+      <c r="C98">
+        <v>1</v>
+      </c>
       <c r="D98" t="s">
         <v>12</v>
       </c>
@@ -12965,7 +13480,10 @@
         <v>398</v>
       </c>
     </row>
-    <row r="99" spans="4:11">
+    <row r="99" spans="3:11">
+      <c r="C99">
+        <v>1</v>
+      </c>
       <c r="D99" t="s">
         <v>12</v>
       </c>
@@ -12991,7 +13509,10 @@
         <v>400</v>
       </c>
     </row>
-    <row r="100" spans="4:11">
+    <row r="100" spans="3:11">
+      <c r="C100">
+        <v>1</v>
+      </c>
       <c r="D100" t="s">
         <v>12</v>
       </c>
@@ -13017,7 +13538,10 @@
         <v>402</v>
       </c>
     </row>
-    <row r="101" spans="4:11">
+    <row r="101" spans="3:11">
+      <c r="C101">
+        <v>1</v>
+      </c>
       <c r="D101" t="s">
         <v>12</v>
       </c>
@@ -13043,7 +13567,10 @@
         <v>404</v>
       </c>
     </row>
-    <row r="102" spans="4:11">
+    <row r="102" spans="3:11">
+      <c r="C102">
+        <v>1</v>
+      </c>
       <c r="D102" t="s">
         <v>12</v>
       </c>
@@ -13069,7 +13596,10 @@
         <v>406</v>
       </c>
     </row>
-    <row r="103" spans="4:11">
+    <row r="103" spans="3:11">
+      <c r="C103">
+        <v>1</v>
+      </c>
       <c r="D103" t="s">
         <v>12</v>
       </c>
@@ -13095,7 +13625,10 @@
         <v>408</v>
       </c>
     </row>
-    <row r="104" spans="4:11">
+    <row r="104" spans="3:11">
+      <c r="C104">
+        <v>1</v>
+      </c>
       <c r="D104" t="s">
         <v>12</v>
       </c>
@@ -13121,7 +13654,10 @@
         <v>410</v>
       </c>
     </row>
-    <row r="105" spans="4:11">
+    <row r="105" spans="3:11">
+      <c r="C105">
+        <v>1</v>
+      </c>
       <c r="D105" t="s">
         <v>12</v>
       </c>
@@ -13147,7 +13683,10 @@
         <v>412</v>
       </c>
     </row>
-    <row r="106" spans="4:11">
+    <row r="106" spans="3:11">
+      <c r="C106">
+        <v>1</v>
+      </c>
       <c r="D106" t="s">
         <v>12</v>
       </c>
@@ -13173,7 +13712,10 @@
         <v>416</v>
       </c>
     </row>
-    <row r="107" spans="4:11">
+    <row r="107" spans="3:11">
+      <c r="C107">
+        <v>1</v>
+      </c>
       <c r="D107" t="s">
         <v>12</v>
       </c>
@@ -13199,7 +13741,10 @@
         <v>420</v>
       </c>
     </row>
-    <row r="108" spans="4:11">
+    <row r="108" spans="3:11">
+      <c r="C108">
+        <v>1</v>
+      </c>
       <c r="D108" t="s">
         <v>12</v>
       </c>
@@ -13225,7 +13770,10 @@
         <v>424</v>
       </c>
     </row>
-    <row r="109" spans="4:11">
+    <row r="109" spans="3:11">
+      <c r="C109">
+        <v>1</v>
+      </c>
       <c r="D109" t="s">
         <v>12</v>
       </c>
@@ -13251,7 +13799,10 @@
         <v>428</v>
       </c>
     </row>
-    <row r="110" spans="4:11">
+    <row r="110" spans="3:11">
+      <c r="C110">
+        <v>1</v>
+      </c>
       <c r="D110" t="s">
         <v>12</v>
       </c>
@@ -13277,7 +13828,10 @@
         <v>432</v>
       </c>
     </row>
-    <row r="111" spans="4:11">
+    <row r="111" spans="3:11">
+      <c r="C111">
+        <v>1</v>
+      </c>
       <c r="D111" t="s">
         <v>12</v>
       </c>
@@ -13303,7 +13857,10 @@
         <v>436</v>
       </c>
     </row>
-    <row r="112" spans="4:11">
+    <row r="112" spans="3:11">
+      <c r="C112">
+        <v>1</v>
+      </c>
       <c r="D112" t="s">
         <v>12</v>
       </c>
@@ -13329,7 +13886,10 @@
         <v>440</v>
       </c>
     </row>
-    <row r="113" spans="4:11">
+    <row r="113" spans="3:11">
+      <c r="C113">
+        <v>1</v>
+      </c>
       <c r="D113" t="s">
         <v>12</v>
       </c>
@@ -13355,7 +13915,10 @@
         <v>444</v>
       </c>
     </row>
-    <row r="114" spans="4:11">
+    <row r="114" spans="3:11">
+      <c r="C114">
+        <v>1</v>
+      </c>
       <c r="D114" t="s">
         <v>12</v>
       </c>
@@ -13381,7 +13944,10 @@
         <v>448</v>
       </c>
     </row>
-    <row r="115" spans="4:11">
+    <row r="115" spans="3:11">
+      <c r="C115">
+        <v>1</v>
+      </c>
       <c r="D115" t="s">
         <v>12</v>
       </c>
@@ -13407,7 +13973,10 @@
         <v>450</v>
       </c>
     </row>
-    <row r="116" spans="4:11">
+    <row r="116" spans="3:11">
+      <c r="C116">
+        <v>1</v>
+      </c>
       <c r="D116" t="s">
         <v>12</v>
       </c>
@@ -13433,7 +14002,10 @@
         <v>454</v>
       </c>
     </row>
-    <row r="117" spans="4:11">
+    <row r="117" spans="3:11">
+      <c r="C117">
+        <v>1</v>
+      </c>
       <c r="D117" t="s">
         <v>12</v>
       </c>
@@ -13459,7 +14031,10 @@
         <v>458</v>
       </c>
     </row>
-    <row r="118" spans="4:11">
+    <row r="118" spans="3:11">
+      <c r="C118">
+        <v>1</v>
+      </c>
       <c r="D118" t="s">
         <v>12</v>
       </c>
@@ -13485,7 +14060,10 @@
         <v>462</v>
       </c>
     </row>
-    <row r="119" spans="4:11">
+    <row r="119" spans="3:11">
+      <c r="C119">
+        <v>1</v>
+      </c>
       <c r="D119" t="s">
         <v>12</v>
       </c>
@@ -13511,7 +14089,10 @@
         <v>466</v>
       </c>
     </row>
-    <row r="120" spans="4:11">
+    <row r="120" spans="3:11">
+      <c r="C120">
+        <v>1</v>
+      </c>
       <c r="D120" t="s">
         <v>12</v>
       </c>
@@ -13537,7 +14118,10 @@
         <v>470</v>
       </c>
     </row>
-    <row r="121" spans="4:11">
+    <row r="121" spans="3:11">
+      <c r="C121">
+        <v>1</v>
+      </c>
       <c r="D121" t="s">
         <v>12</v>
       </c>
@@ -13563,7 +14147,10 @@
         <v>474</v>
       </c>
     </row>
-    <row r="122" spans="4:11">
+    <row r="122" spans="3:11">
+      <c r="C122">
+        <v>1</v>
+      </c>
       <c r="D122" t="s">
         <v>12</v>
       </c>
@@ -13589,7 +14176,10 @@
         <v>478</v>
       </c>
     </row>
-    <row r="123" spans="4:11">
+    <row r="123" spans="3:11">
+      <c r="C123">
+        <v>1</v>
+      </c>
       <c r="D123" t="s">
         <v>12</v>
       </c>
@@ -13615,7 +14205,10 @@
         <v>482</v>
       </c>
     </row>
-    <row r="124" spans="4:11">
+    <row r="124" spans="3:11">
+      <c r="C124">
+        <v>1</v>
+      </c>
       <c r="D124" t="s">
         <v>12</v>
       </c>
@@ -13641,7 +14234,10 @@
         <v>486</v>
       </c>
     </row>
-    <row r="125" spans="4:11">
+    <row r="125" spans="3:11">
+      <c r="C125">
+        <v>1</v>
+      </c>
       <c r="D125" t="s">
         <v>12</v>
       </c>
@@ -13667,7 +14263,10 @@
         <v>490</v>
       </c>
     </row>
-    <row r="126" spans="4:11">
+    <row r="126" spans="3:11">
+      <c r="C126">
+        <v>1</v>
+      </c>
       <c r="D126" t="s">
         <v>12</v>
       </c>
@@ -13693,7 +14292,10 @@
         <v>492</v>
       </c>
     </row>
-    <row r="127" spans="4:11">
+    <row r="127" spans="3:11">
+      <c r="C127">
+        <v>1</v>
+      </c>
       <c r="D127" t="s">
         <v>12</v>
       </c>
@@ -13719,7 +14321,10 @@
         <v>496</v>
       </c>
     </row>
-    <row r="128" spans="4:11">
+    <row r="128" spans="3:11">
+      <c r="C128">
+        <v>1</v>
+      </c>
       <c r="D128" t="s">
         <v>12</v>
       </c>
@@ -13745,7 +14350,10 @@
         <v>500</v>
       </c>
     </row>
-    <row r="129" spans="4:11">
+    <row r="129" spans="3:11">
+      <c r="C129">
+        <v>1</v>
+      </c>
       <c r="D129" t="s">
         <v>12</v>
       </c>
@@ -13771,7 +14379,10 @@
         <v>504</v>
       </c>
     </row>
-    <row r="130" spans="4:11">
+    <row r="130" spans="3:11">
+      <c r="C130">
+        <v>1</v>
+      </c>
       <c r="D130" t="s">
         <v>12</v>
       </c>
@@ -13797,7 +14408,10 @@
         <v>508</v>
       </c>
     </row>
-    <row r="131" spans="4:11">
+    <row r="131" spans="3:11">
+      <c r="C131">
+        <v>1</v>
+      </c>
       <c r="D131" t="s">
         <v>12</v>
       </c>
@@ -13823,7 +14437,10 @@
         <v>512</v>
       </c>
     </row>
-    <row r="132" spans="4:11">
+    <row r="132" spans="3:11">
+      <c r="C132">
+        <v>1</v>
+      </c>
       <c r="D132" t="s">
         <v>12</v>
       </c>
@@ -13849,7 +14466,10 @@
         <v>516</v>
       </c>
     </row>
-    <row r="133" spans="4:11">
+    <row r="133" spans="3:11">
+      <c r="C133">
+        <v>1</v>
+      </c>
       <c r="D133" t="s">
         <v>12</v>
       </c>
@@ -13875,7 +14495,10 @@
         <v>520</v>
       </c>
     </row>
-    <row r="134" spans="4:11">
+    <row r="134" spans="3:11">
+      <c r="C134">
+        <v>1</v>
+      </c>
       <c r="D134" t="s">
         <v>12</v>
       </c>
@@ -13901,7 +14524,10 @@
         <v>524</v>
       </c>
     </row>
-    <row r="135" spans="4:11">
+    <row r="135" spans="3:11">
+      <c r="C135">
+        <v>1</v>
+      </c>
       <c r="D135" t="s">
         <v>12</v>
       </c>
@@ -13927,7 +14553,10 @@
         <v>526</v>
       </c>
     </row>
-    <row r="136" spans="4:11">
+    <row r="136" spans="3:11">
+      <c r="C136">
+        <v>1</v>
+      </c>
       <c r="D136" t="s">
         <v>12</v>
       </c>
@@ -13953,7 +14582,10 @@
         <v>528</v>
       </c>
     </row>
-    <row r="137" spans="4:11">
+    <row r="137" spans="3:11">
+      <c r="C137">
+        <v>1</v>
+      </c>
       <c r="D137" t="s">
         <v>12</v>
       </c>
@@ -13979,7 +14611,10 @@
         <v>530</v>
       </c>
     </row>
-    <row r="138" spans="4:11">
+    <row r="138" spans="3:11">
+      <c r="C138">
+        <v>1</v>
+      </c>
       <c r="D138" t="s">
         <v>12</v>
       </c>
@@ -14005,7 +14640,10 @@
         <v>532</v>
       </c>
     </row>
-    <row r="139" spans="4:11">
+    <row r="139" spans="3:11">
+      <c r="C139">
+        <v>1</v>
+      </c>
       <c r="D139" t="s">
         <v>12</v>
       </c>
@@ -14031,7 +14669,10 @@
         <v>534</v>
       </c>
     </row>
-    <row r="140" spans="4:11">
+    <row r="140" spans="3:11">
+      <c r="C140">
+        <v>1</v>
+      </c>
       <c r="D140" t="s">
         <v>12</v>
       </c>
@@ -14057,7 +14698,10 @@
         <v>538</v>
       </c>
     </row>
-    <row r="141" spans="4:11">
+    <row r="141" spans="3:11">
+      <c r="C141">
+        <v>1</v>
+      </c>
       <c r="D141" t="s">
         <v>12</v>
       </c>
@@ -14083,7 +14727,10 @@
         <v>540</v>
       </c>
     </row>
-    <row r="142" spans="4:11">
+    <row r="142" spans="3:11">
+      <c r="C142">
+        <v>1</v>
+      </c>
       <c r="D142" t="s">
         <v>12</v>
       </c>
@@ -14109,7 +14756,10 @@
         <v>544</v>
       </c>
     </row>
-    <row r="143" spans="4:11">
+    <row r="143" spans="3:11">
+      <c r="C143">
+        <v>1</v>
+      </c>
       <c r="D143" t="s">
         <v>12</v>
       </c>
@@ -14135,7 +14785,10 @@
         <v>548</v>
       </c>
     </row>
-    <row r="144" spans="4:11">
+    <row r="144" spans="3:11">
+      <c r="C144">
+        <v>1</v>
+      </c>
       <c r="D144" t="s">
         <v>12</v>
       </c>
@@ -14161,7 +14814,10 @@
         <v>552</v>
       </c>
     </row>
-    <row r="145" spans="4:11">
+    <row r="145" spans="3:11">
+      <c r="C145">
+        <v>1</v>
+      </c>
       <c r="D145" t="s">
         <v>12</v>
       </c>
@@ -14187,7 +14843,10 @@
         <v>556</v>
       </c>
     </row>
-    <row r="146" spans="4:11">
+    <row r="146" spans="3:11">
+      <c r="C146">
+        <v>1</v>
+      </c>
       <c r="D146" t="s">
         <v>12</v>
       </c>
@@ -14213,7 +14872,10 @@
         <v>560</v>
       </c>
     </row>
-    <row r="147" spans="4:11">
+    <row r="147" spans="3:11">
+      <c r="C147">
+        <v>1</v>
+      </c>
       <c r="D147" t="s">
         <v>12</v>
       </c>
@@ -14239,7 +14901,10 @@
         <v>564</v>
       </c>
     </row>
-    <row r="148" spans="4:11">
+    <row r="148" spans="3:11">
+      <c r="C148">
+        <v>1</v>
+      </c>
       <c r="D148" t="s">
         <v>12</v>
       </c>
@@ -14265,7 +14930,10 @@
         <v>568</v>
       </c>
     </row>
-    <row r="149" spans="4:11">
+    <row r="149" spans="3:11">
+      <c r="C149">
+        <v>1</v>
+      </c>
       <c r="D149" t="s">
         <v>12</v>
       </c>
@@ -14291,7 +14959,10 @@
         <v>572</v>
       </c>
     </row>
-    <row r="150" spans="4:11">
+    <row r="150" spans="3:11">
+      <c r="C150">
+        <v>1</v>
+      </c>
       <c r="D150" t="s">
         <v>12</v>
       </c>
@@ -14317,7 +14988,10 @@
         <v>576</v>
       </c>
     </row>
-    <row r="151" spans="4:11">
+    <row r="151" spans="3:11">
+      <c r="C151">
+        <v>1</v>
+      </c>
       <c r="D151" t="s">
         <v>12</v>
       </c>
@@ -14343,7 +15017,10 @@
         <v>580</v>
       </c>
     </row>
-    <row r="152" spans="4:11">
+    <row r="152" spans="3:11">
+      <c r="C152">
+        <v>1</v>
+      </c>
       <c r="D152" t="s">
         <v>12</v>
       </c>
@@ -14369,7 +15046,10 @@
         <v>584</v>
       </c>
     </row>
-    <row r="153" spans="4:11">
+    <row r="153" spans="3:11">
+      <c r="C153">
+        <v>1</v>
+      </c>
       <c r="D153" t="s">
         <v>12</v>
       </c>
@@ -14395,7 +15075,10 @@
         <v>588</v>
       </c>
     </row>
-    <row r="154" spans="4:11">
+    <row r="154" spans="3:11">
+      <c r="C154">
+        <v>1</v>
+      </c>
       <c r="D154" t="s">
         <v>12</v>
       </c>
@@ -14421,7 +15104,10 @@
         <v>592</v>
       </c>
     </row>
-    <row r="155" spans="4:11">
+    <row r="155" spans="3:11">
+      <c r="C155">
+        <v>1</v>
+      </c>
       <c r="D155" t="s">
         <v>12</v>
       </c>
@@ -14447,7 +15133,10 @@
         <v>595</v>
       </c>
     </row>
-    <row r="156" spans="4:11">
+    <row r="156" spans="3:11">
+      <c r="C156">
+        <v>1</v>
+      </c>
       <c r="D156" t="s">
         <v>12</v>
       </c>
@@ -14473,7 +15162,10 @@
         <v>598</v>
       </c>
     </row>
-    <row r="157" spans="4:11">
+    <row r="157" spans="3:11">
+      <c r="C157">
+        <v>1</v>
+      </c>
       <c r="D157" t="s">
         <v>12</v>
       </c>
@@ -14499,7 +15191,10 @@
         <v>602</v>
       </c>
     </row>
-    <row r="158" spans="4:11">
+    <row r="158" spans="3:11">
+      <c r="C158">
+        <v>1</v>
+      </c>
       <c r="D158" t="s">
         <v>12</v>
       </c>
@@ -14525,7 +15220,10 @@
         <v>606</v>
       </c>
     </row>
-    <row r="159" spans="4:11">
+    <row r="159" spans="3:11">
+      <c r="C159">
+        <v>1</v>
+      </c>
       <c r="D159" t="s">
         <v>12</v>
       </c>
@@ -14551,7 +15249,10 @@
         <v>610</v>
       </c>
     </row>
-    <row r="160" spans="4:11">
+    <row r="160" spans="3:11">
+      <c r="C160">
+        <v>1</v>
+      </c>
       <c r="D160" t="s">
         <v>12</v>
       </c>
@@ -14577,7 +15278,10 @@
         <v>613</v>
       </c>
     </row>
-    <row r="161" spans="4:11">
+    <row r="161" spans="3:11">
+      <c r="C161">
+        <v>1</v>
+      </c>
       <c r="D161" t="s">
         <v>12</v>
       </c>
@@ -14603,7 +15307,10 @@
         <v>616</v>
       </c>
     </row>
-    <row r="162" spans="4:11">
+    <row r="162" spans="3:11">
+      <c r="C162">
+        <v>1</v>
+      </c>
       <c r="D162" t="s">
         <v>12</v>
       </c>
@@ -14629,7 +15336,10 @@
         <v>619</v>
       </c>
     </row>
-    <row r="163" spans="4:11">
+    <row r="163" spans="3:11">
+      <c r="C163">
+        <v>1</v>
+      </c>
       <c r="D163" t="s">
         <v>12</v>
       </c>
@@ -14655,7 +15365,10 @@
         <v>623</v>
       </c>
     </row>
-    <row r="164" spans="4:11">
+    <row r="164" spans="3:11">
+      <c r="C164">
+        <v>1</v>
+      </c>
       <c r="D164" t="s">
         <v>12</v>
       </c>
@@ -14681,7 +15394,10 @@
         <v>626</v>
       </c>
     </row>
-    <row r="165" spans="4:11">
+    <row r="165" spans="3:11">
+      <c r="C165">
+        <v>1</v>
+      </c>
       <c r="D165" t="s">
         <v>12</v>
       </c>
@@ -14707,7 +15423,10 @@
         <v>629</v>
       </c>
     </row>
-    <row r="166" spans="4:11">
+    <row r="166" spans="3:11">
+      <c r="C166">
+        <v>1</v>
+      </c>
       <c r="D166" t="s">
         <v>12</v>
       </c>
@@ -14733,7 +15452,10 @@
         <v>632</v>
       </c>
     </row>
-    <row r="167" spans="4:11">
+    <row r="167" spans="3:11">
+      <c r="C167">
+        <v>1</v>
+      </c>
       <c r="D167" t="s">
         <v>12</v>
       </c>
@@ -14759,7 +15481,10 @@
         <v>635</v>
       </c>
     </row>
-    <row r="168" spans="4:11">
+    <row r="168" spans="3:11">
+      <c r="C168">
+        <v>1</v>
+      </c>
       <c r="D168" t="s">
         <v>12</v>
       </c>
@@ -14785,7 +15510,10 @@
         <v>638</v>
       </c>
     </row>
-    <row r="169" spans="4:11">
+    <row r="169" spans="3:11">
+      <c r="C169">
+        <v>1</v>
+      </c>
       <c r="D169" t="s">
         <v>12</v>
       </c>
@@ -14811,7 +15539,10 @@
         <v>641</v>
       </c>
     </row>
-    <row r="170" spans="4:11">
+    <row r="170" spans="3:11">
+      <c r="C170">
+        <v>1</v>
+      </c>
       <c r="D170" t="s">
         <v>12</v>
       </c>
@@ -14837,7 +15568,10 @@
         <v>645</v>
       </c>
     </row>
-    <row r="171" spans="4:11">
+    <row r="171" spans="3:11">
+      <c r="C171">
+        <v>1</v>
+      </c>
       <c r="D171" t="s">
         <v>12</v>
       </c>
@@ -14863,7 +15597,10 @@
         <v>647</v>
       </c>
     </row>
-    <row r="172" spans="4:11">
+    <row r="172" spans="3:11">
+      <c r="C172">
+        <v>1</v>
+      </c>
       <c r="D172" t="s">
         <v>12</v>
       </c>
@@ -14889,7 +15626,10 @@
         <v>649</v>
       </c>
     </row>
-    <row r="173" spans="4:11">
+    <row r="173" spans="3:11">
+      <c r="C173">
+        <v>1</v>
+      </c>
       <c r="D173" t="s">
         <v>12</v>
       </c>
@@ -14915,7 +15655,10 @@
         <v>651</v>
       </c>
     </row>
-    <row r="174" spans="4:11">
+    <row r="174" spans="3:11">
+      <c r="C174">
+        <v>1</v>
+      </c>
       <c r="D174" t="s">
         <v>12</v>
       </c>
@@ -14941,7 +15684,10 @@
         <v>653</v>
       </c>
     </row>
-    <row r="175" spans="4:11">
+    <row r="175" spans="3:11">
+      <c r="C175">
+        <v>1</v>
+      </c>
       <c r="D175" t="s">
         <v>12</v>
       </c>
@@ -14967,7 +15713,10 @@
         <v>655</v>
       </c>
     </row>
-    <row r="176" spans="4:11">
+    <row r="176" spans="3:11">
+      <c r="C176">
+        <v>1</v>
+      </c>
       <c r="D176" t="s">
         <v>12</v>
       </c>
@@ -14993,7 +15742,10 @@
         <v>657</v>
       </c>
     </row>
-    <row r="177" spans="4:11">
+    <row r="177" spans="3:11">
+      <c r="C177">
+        <v>1</v>
+      </c>
       <c r="D177" t="s">
         <v>12</v>
       </c>
@@ -15019,7 +15771,10 @@
         <v>659</v>
       </c>
     </row>
-    <row r="178" spans="4:11">
+    <row r="178" spans="3:11">
+      <c r="C178">
+        <v>1</v>
+      </c>
       <c r="D178" t="s">
         <v>12</v>
       </c>
@@ -15045,7 +15800,10 @@
         <v>661</v>
       </c>
     </row>
-    <row r="179" spans="4:11">
+    <row r="179" spans="3:11">
+      <c r="C179">
+        <v>1</v>
+      </c>
       <c r="D179" t="s">
         <v>12</v>
       </c>
@@ -15071,7 +15829,10 @@
         <v>663</v>
       </c>
     </row>
-    <row r="180" spans="4:11">
+    <row r="180" spans="3:11">
+      <c r="C180">
+        <v>1</v>
+      </c>
       <c r="D180" t="s">
         <v>12</v>
       </c>
@@ -15097,7 +15858,10 @@
         <v>665</v>
       </c>
     </row>
-    <row r="181" spans="4:11">
+    <row r="181" spans="3:11">
+      <c r="C181">
+        <v>1</v>
+      </c>
       <c r="D181" t="s">
         <v>12</v>
       </c>
@@ -15123,7 +15887,10 @@
         <v>667</v>
       </c>
     </row>
-    <row r="182" spans="4:11">
+    <row r="182" spans="3:11">
+      <c r="C182">
+        <v>1</v>
+      </c>
       <c r="D182" t="s">
         <v>12</v>
       </c>
@@ -15149,7 +15916,10 @@
         <v>669</v>
       </c>
     </row>
-    <row r="183" spans="4:11">
+    <row r="183" spans="3:11">
+      <c r="C183">
+        <v>1</v>
+      </c>
       <c r="D183" t="s">
         <v>12</v>
       </c>
@@ -15175,7 +15945,10 @@
         <v>671</v>
       </c>
     </row>
-    <row r="184" spans="4:11">
+    <row r="184" spans="3:11">
+      <c r="C184">
+        <v>1</v>
+      </c>
       <c r="D184" t="s">
         <v>12</v>
       </c>
@@ -15201,7 +15974,10 @@
         <v>675</v>
       </c>
     </row>
-    <row r="185" spans="4:11">
+    <row r="185" spans="3:11">
+      <c r="C185">
+        <v>1</v>
+      </c>
       <c r="D185" t="s">
         <v>12</v>
       </c>
@@ -15227,7 +16003,10 @@
         <v>679</v>
       </c>
     </row>
-    <row r="186" spans="4:11">
+    <row r="186" spans="3:11">
+      <c r="C186">
+        <v>1</v>
+      </c>
       <c r="D186" t="s">
         <v>12</v>
       </c>
@@ -15253,7 +16032,10 @@
         <v>683</v>
       </c>
     </row>
-    <row r="187" spans="4:11">
+    <row r="187" spans="3:11">
+      <c r="C187">
+        <v>1</v>
+      </c>
       <c r="D187" t="s">
         <v>12</v>
       </c>
@@ -15279,7 +16061,10 @@
         <v>687</v>
       </c>
     </row>
-    <row r="188" spans="4:11">
+    <row r="188" spans="3:11">
+      <c r="C188">
+        <v>1</v>
+      </c>
       <c r="D188" t="s">
         <v>12</v>
       </c>
@@ -15305,7 +16090,10 @@
         <v>691</v>
       </c>
     </row>
-    <row r="189" spans="4:11">
+    <row r="189" spans="3:11">
+      <c r="C189">
+        <v>1</v>
+      </c>
       <c r="D189" t="s">
         <v>12</v>
       </c>
@@ -15331,7 +16119,10 @@
         <v>695</v>
       </c>
     </row>
-    <row r="190" spans="4:11">
+    <row r="190" spans="3:11">
+      <c r="C190">
+        <v>1</v>
+      </c>
       <c r="D190" t="s">
         <v>12</v>
       </c>
@@ -15357,7 +16148,10 @@
         <v>699</v>
       </c>
     </row>
-    <row r="191" spans="4:11">
+    <row r="191" spans="3:11">
+      <c r="C191">
+        <v>1</v>
+      </c>
       <c r="D191" t="s">
         <v>12</v>
       </c>
@@ -15383,7 +16177,10 @@
         <v>703</v>
       </c>
     </row>
-    <row r="192" spans="4:11">
+    <row r="192" spans="3:11">
+      <c r="C192">
+        <v>1</v>
+      </c>
       <c r="D192" t="s">
         <v>12</v>
       </c>
@@ -15409,7 +16206,10 @@
         <v>707</v>
       </c>
     </row>
-    <row r="193" spans="4:11">
+    <row r="193" spans="3:11">
+      <c r="C193">
+        <v>1</v>
+      </c>
       <c r="D193" t="s">
         <v>12</v>
       </c>
@@ -15435,7 +16235,10 @@
         <v>711</v>
       </c>
     </row>
-    <row r="194" spans="4:11">
+    <row r="194" spans="3:11">
+      <c r="C194">
+        <v>1</v>
+      </c>
       <c r="D194" t="s">
         <v>12</v>
       </c>
@@ -15461,7 +16264,10 @@
         <v>715</v>
       </c>
     </row>
-    <row r="195" spans="4:11">
+    <row r="195" spans="3:11">
+      <c r="C195">
+        <v>1</v>
+      </c>
       <c r="D195" t="s">
         <v>12</v>
       </c>
@@ -15487,7 +16293,10 @@
         <v>719</v>
       </c>
     </row>
-    <row r="196" spans="4:11">
+    <row r="196" spans="3:11">
+      <c r="C196">
+        <v>1</v>
+      </c>
       <c r="D196" t="s">
         <v>12</v>
       </c>
@@ -15513,7 +16322,10 @@
         <v>723</v>
       </c>
     </row>
-    <row r="197" spans="4:11">
+    <row r="197" spans="3:11">
+      <c r="C197">
+        <v>1</v>
+      </c>
       <c r="D197" t="s">
         <v>12</v>
       </c>
@@ -15539,7 +16351,10 @@
         <v>727</v>
       </c>
     </row>
-    <row r="198" spans="4:11">
+    <row r="198" spans="3:11">
+      <c r="C198">
+        <v>1</v>
+      </c>
       <c r="D198" t="s">
         <v>12</v>
       </c>
@@ -15565,7 +16380,10 @@
         <v>731</v>
       </c>
     </row>
-    <row r="199" spans="4:11">
+    <row r="199" spans="3:11">
+      <c r="C199">
+        <v>1</v>
+      </c>
       <c r="D199" t="s">
         <v>12</v>
       </c>
@@ -15591,7 +16409,10 @@
         <v>735</v>
       </c>
     </row>
-    <row r="200" spans="4:11">
+    <row r="200" spans="3:11">
+      <c r="C200">
+        <v>1</v>
+      </c>
       <c r="D200" t="s">
         <v>12</v>
       </c>
@@ -15617,7 +16438,10 @@
         <v>739</v>
       </c>
     </row>
-    <row r="201" spans="4:11">
+    <row r="201" spans="3:11">
+      <c r="C201">
+        <v>1</v>
+      </c>
       <c r="D201" t="s">
         <v>12</v>
       </c>
@@ -15643,7 +16467,10 @@
         <v>743</v>
       </c>
     </row>
-    <row r="202" spans="4:11">
+    <row r="202" spans="3:11">
+      <c r="C202">
+        <v>1</v>
+      </c>
       <c r="D202" t="s">
         <v>12</v>
       </c>
@@ -15669,7 +16496,10 @@
         <v>748</v>
       </c>
     </row>
-    <row r="203" spans="4:11">
+    <row r="203" spans="3:11">
+      <c r="C203">
+        <v>1</v>
+      </c>
       <c r="D203" t="s">
         <v>12</v>
       </c>
@@ -15695,7 +16525,10 @@
         <v>751</v>
       </c>
     </row>
-    <row r="204" spans="4:11">
+    <row r="204" spans="3:11">
+      <c r="C204">
+        <v>1</v>
+      </c>
       <c r="D204" t="s">
         <v>12</v>
       </c>
@@ -15721,7 +16554,10 @@
         <v>755</v>
       </c>
     </row>
-    <row r="205" spans="4:11">
+    <row r="205" spans="3:11">
+      <c r="C205">
+        <v>1</v>
+      </c>
       <c r="D205" t="s">
         <v>12</v>
       </c>
@@ -15747,7 +16583,10 @@
         <v>758</v>
       </c>
     </row>
-    <row r="206" spans="4:11">
+    <row r="206" spans="3:11">
+      <c r="C206">
+        <v>1</v>
+      </c>
       <c r="D206" t="s">
         <v>12</v>
       </c>
@@ -15773,7 +16612,10 @@
         <v>761</v>
       </c>
     </row>
-    <row r="207" spans="4:11">
+    <row r="207" spans="3:11">
+      <c r="C207">
+        <v>1</v>
+      </c>
       <c r="D207" t="s">
         <v>12</v>
       </c>
@@ -15799,7 +16641,10 @@
         <v>764</v>
       </c>
     </row>
-    <row r="208" spans="4:11">
+    <row r="208" spans="3:11">
+      <c r="C208">
+        <v>1</v>
+      </c>
       <c r="D208" t="s">
         <v>12</v>
       </c>
@@ -15825,7 +16670,10 @@
         <v>767</v>
       </c>
     </row>
-    <row r="209" spans="4:11">
+    <row r="209" spans="3:11">
+      <c r="C209">
+        <v>1</v>
+      </c>
       <c r="D209" t="s">
         <v>12</v>
       </c>
@@ -15851,7 +16699,10 @@
         <v>770</v>
       </c>
     </row>
-    <row r="210" spans="4:11">
+    <row r="210" spans="3:11">
+      <c r="C210">
+        <v>1</v>
+      </c>
       <c r="D210" t="s">
         <v>12</v>
       </c>
@@ -15877,7 +16728,10 @@
         <v>773</v>
       </c>
     </row>
-    <row r="211" spans="4:11">
+    <row r="211" spans="3:11">
+      <c r="C211">
+        <v>1</v>
+      </c>
       <c r="D211" t="s">
         <v>12</v>
       </c>
@@ -15903,7 +16757,10 @@
         <v>776</v>
       </c>
     </row>
-    <row r="212" spans="4:11">
+    <row r="212" spans="3:11">
+      <c r="C212">
+        <v>1</v>
+      </c>
       <c r="D212" t="s">
         <v>12</v>
       </c>
@@ -15929,7 +16786,10 @@
         <v>779</v>
       </c>
     </row>
-    <row r="213" spans="4:11">
+    <row r="213" spans="3:11">
+      <c r="C213">
+        <v>1</v>
+      </c>
       <c r="D213" t="s">
         <v>12</v>
       </c>
@@ -15955,7 +16815,10 @@
         <v>782</v>
       </c>
     </row>
-    <row r="214" spans="4:11">
+    <row r="214" spans="3:11">
+      <c r="C214">
+        <v>1</v>
+      </c>
       <c r="D214" t="s">
         <v>12</v>
       </c>
@@ -15981,7 +16844,10 @@
         <v>786</v>
       </c>
     </row>
-    <row r="215" spans="4:11">
+    <row r="215" spans="3:11">
+      <c r="C215">
+        <v>1</v>
+      </c>
       <c r="D215" t="s">
         <v>12</v>
       </c>
@@ -16007,7 +16873,10 @@
         <v>790</v>
       </c>
     </row>
-    <row r="216" spans="4:11">
+    <row r="216" spans="3:11">
+      <c r="C216">
+        <v>1</v>
+      </c>
       <c r="D216" t="s">
         <v>12</v>
       </c>
@@ -16033,7 +16902,10 @@
         <v>794</v>
       </c>
     </row>
-    <row r="217" spans="4:11">
+    <row r="217" spans="3:11">
+      <c r="C217">
+        <v>1</v>
+      </c>
       <c r="D217" t="s">
         <v>12</v>
       </c>
@@ -16059,7 +16931,10 @@
         <v>798</v>
       </c>
     </row>
-    <row r="218" spans="4:11">
+    <row r="218" spans="3:11">
+      <c r="C218">
+        <v>1</v>
+      </c>
       <c r="D218" t="s">
         <v>12</v>
       </c>
@@ -16085,7 +16960,10 @@
         <v>802</v>
       </c>
     </row>
-    <row r="219" spans="4:11">
+    <row r="219" spans="3:11">
+      <c r="C219">
+        <v>1</v>
+      </c>
       <c r="D219" t="s">
         <v>12</v>
       </c>
@@ -16111,7 +16989,10 @@
         <v>805</v>
       </c>
     </row>
-    <row r="220" spans="4:11">
+    <row r="220" spans="3:11">
+      <c r="C220">
+        <v>1</v>
+      </c>
       <c r="D220" t="s">
         <v>12</v>
       </c>
@@ -16137,7 +17018,10 @@
         <v>808</v>
       </c>
     </row>
-    <row r="221" spans="4:11">
+    <row r="221" spans="3:11">
+      <c r="C221">
+        <v>1</v>
+      </c>
       <c r="D221" t="s">
         <v>12</v>
       </c>
@@ -16163,7 +17047,10 @@
         <v>811</v>
       </c>
     </row>
-    <row r="222" spans="4:11">
+    <row r="222" spans="3:11">
+      <c r="C222">
+        <v>1</v>
+      </c>
       <c r="D222" t="s">
         <v>12</v>
       </c>
@@ -16189,7 +17076,10 @@
         <v>814</v>
       </c>
     </row>
-    <row r="223" spans="4:11">
+    <row r="223" spans="3:11">
+      <c r="C223">
+        <v>1</v>
+      </c>
       <c r="D223" t="s">
         <v>12</v>
       </c>
@@ -16215,7 +17105,10 @@
         <v>817</v>
       </c>
     </row>
-    <row r="224" spans="4:11">
+    <row r="224" spans="3:11">
+      <c r="C224">
+        <v>1</v>
+      </c>
       <c r="D224" t="s">
         <v>12</v>
       </c>
@@ -16241,7 +17134,10 @@
         <v>821</v>
       </c>
     </row>
-    <row r="225" spans="4:11">
+    <row r="225" spans="3:11">
+      <c r="C225">
+        <v>1</v>
+      </c>
       <c r="D225" t="s">
         <v>12</v>
       </c>
@@ -16267,7 +17163,10 @@
         <v>824</v>
       </c>
     </row>
-    <row r="226" spans="4:11">
+    <row r="226" spans="3:11">
+      <c r="C226">
+        <v>1</v>
+      </c>
       <c r="D226" t="s">
         <v>12</v>
       </c>
@@ -16293,7 +17192,10 @@
         <v>827</v>
       </c>
     </row>
-    <row r="227" spans="4:11">
+    <row r="227" spans="3:11">
+      <c r="C227">
+        <v>1</v>
+      </c>
       <c r="D227" t="s">
         <v>12</v>
       </c>
@@ -16319,7 +17221,10 @@
         <v>830</v>
       </c>
     </row>
-    <row r="228" spans="4:11">
+    <row r="228" spans="3:11">
+      <c r="C228">
+        <v>1</v>
+      </c>
       <c r="D228" t="s">
         <v>12</v>
       </c>
@@ -16345,7 +17250,10 @@
         <v>833</v>
       </c>
     </row>
-    <row r="229" spans="4:11">
+    <row r="229" spans="3:11">
+      <c r="C229">
+        <v>1</v>
+      </c>
       <c r="D229" t="s">
         <v>12</v>
       </c>
@@ -16371,7 +17279,10 @@
         <v>836</v>
       </c>
     </row>
-    <row r="230" spans="4:11">
+    <row r="230" spans="3:11">
+      <c r="C230">
+        <v>1</v>
+      </c>
       <c r="D230" t="s">
         <v>12</v>
       </c>
@@ -16397,7 +17308,10 @@
         <v>839</v>
       </c>
     </row>
-    <row r="231" spans="4:11">
+    <row r="231" spans="3:11">
+      <c r="C231">
+        <v>1</v>
+      </c>
       <c r="D231" t="s">
         <v>12</v>
       </c>
@@ -16423,7 +17337,10 @@
         <v>842</v>
       </c>
     </row>
-    <row r="232" spans="4:11">
+    <row r="232" spans="3:11">
+      <c r="C232">
+        <v>1</v>
+      </c>
       <c r="D232" t="s">
         <v>12</v>
       </c>
@@ -16449,7 +17366,10 @@
         <v>845</v>
       </c>
     </row>
-    <row r="233" spans="4:11">
+    <row r="233" spans="3:11">
+      <c r="C233">
+        <v>1</v>
+      </c>
       <c r="D233" t="s">
         <v>12</v>
       </c>
@@ -16475,7 +17395,10 @@
         <v>848</v>
       </c>
     </row>
-    <row r="234" spans="4:11">
+    <row r="234" spans="3:11">
+      <c r="C234">
+        <v>1</v>
+      </c>
       <c r="D234" t="s">
         <v>12</v>
       </c>
@@ -16501,7 +17424,10 @@
         <v>851</v>
       </c>
     </row>
-    <row r="235" spans="4:11">
+    <row r="235" spans="3:11">
+      <c r="C235">
+        <v>1</v>
+      </c>
       <c r="D235" t="s">
         <v>12</v>
       </c>
@@ -16527,7 +17453,10 @@
         <v>854</v>
       </c>
     </row>
-    <row r="236" spans="4:11">
+    <row r="236" spans="3:11">
+      <c r="C236">
+        <v>1</v>
+      </c>
       <c r="D236" t="s">
         <v>12</v>
       </c>
@@ -16553,7 +17482,10 @@
         <v>856</v>
       </c>
     </row>
-    <row r="237" spans="4:11">
+    <row r="237" spans="3:11">
+      <c r="C237">
+        <v>1</v>
+      </c>
       <c r="D237" t="s">
         <v>12</v>
       </c>
@@ -16579,7 +17511,10 @@
         <v>858</v>
       </c>
     </row>
-    <row r="238" spans="4:11">
+    <row r="238" spans="3:11">
+      <c r="C238">
+        <v>1</v>
+      </c>
       <c r="D238" t="s">
         <v>12</v>
       </c>
@@ -16605,7 +17540,10 @@
         <v>860</v>
       </c>
     </row>
-    <row r="239" spans="4:11">
+    <row r="239" spans="3:11">
+      <c r="C239">
+        <v>1</v>
+      </c>
       <c r="D239" t="s">
         <v>12</v>
       </c>
@@ -16631,7 +17569,10 @@
         <v>864</v>
       </c>
     </row>
-    <row r="240" spans="4:11">
+    <row r="240" spans="3:11">
+      <c r="C240">
+        <v>1</v>
+      </c>
       <c r="D240" t="s">
         <v>12</v>
       </c>
@@ -16657,7 +17598,10 @@
         <v>866</v>
       </c>
     </row>
-    <row r="241" spans="4:11">
+    <row r="241" spans="3:11">
+      <c r="C241">
+        <v>1</v>
+      </c>
       <c r="D241" t="s">
         <v>12</v>
       </c>
@@ -16683,7 +17627,10 @@
         <v>870</v>
       </c>
     </row>
-    <row r="242" spans="4:11">
+    <row r="242" spans="3:11">
+      <c r="C242">
+        <v>1</v>
+      </c>
       <c r="D242" t="s">
         <v>12</v>
       </c>
@@ -16709,7 +17656,10 @@
         <v>874</v>
       </c>
     </row>
-    <row r="243" spans="4:11">
+    <row r="243" spans="3:11">
+      <c r="C243">
+        <v>1</v>
+      </c>
       <c r="D243" t="s">
         <v>12</v>
       </c>
@@ -16735,7 +17685,10 @@
         <v>876</v>
       </c>
     </row>
-    <row r="244" spans="4:11">
+    <row r="244" spans="3:11">
+      <c r="C244">
+        <v>1</v>
+      </c>
       <c r="D244" t="s">
         <v>12</v>
       </c>
@@ -16761,7 +17714,10 @@
         <v>878</v>
       </c>
     </row>
-    <row r="245" spans="4:11">
+    <row r="245" spans="3:11">
+      <c r="C245">
+        <v>1</v>
+      </c>
       <c r="D245" t="s">
         <v>12</v>
       </c>
@@ -16787,7 +17743,10 @@
         <v>880</v>
       </c>
     </row>
-    <row r="246" spans="4:11">
+    <row r="246" spans="3:11">
+      <c r="C246">
+        <v>1</v>
+      </c>
       <c r="D246" t="s">
         <v>12</v>
       </c>
@@ -16813,7 +17772,10 @@
         <v>882</v>
       </c>
     </row>
-    <row r="247" spans="4:11">
+    <row r="247" spans="3:11">
+      <c r="C247">
+        <v>1</v>
+      </c>
       <c r="D247" t="s">
         <v>12</v>
       </c>
@@ -16839,7 +17801,10 @@
         <v>884</v>
       </c>
     </row>
-    <row r="248" spans="4:11">
+    <row r="248" spans="3:11">
+      <c r="C248">
+        <v>1</v>
+      </c>
       <c r="D248" t="s">
         <v>12</v>
       </c>
@@ -16865,7 +17830,10 @@
         <v>886</v>
       </c>
     </row>
-    <row r="249" spans="4:11">
+    <row r="249" spans="3:11">
+      <c r="C249">
+        <v>1</v>
+      </c>
       <c r="D249" t="s">
         <v>12</v>
       </c>
@@ -16891,7 +17859,10 @@
         <v>890</v>
       </c>
     </row>
-    <row r="250" spans="4:11">
+    <row r="250" spans="3:11">
+      <c r="C250">
+        <v>1</v>
+      </c>
       <c r="D250" t="s">
         <v>12</v>
       </c>
@@ -16917,7 +17888,10 @@
         <v>893</v>
       </c>
     </row>
-    <row r="251" spans="4:11">
+    <row r="251" spans="3:11">
+      <c r="C251">
+        <v>1</v>
+      </c>
       <c r="D251" t="s">
         <v>12</v>
       </c>
@@ -16943,7 +17917,10 @@
         <v>895</v>
       </c>
     </row>
-    <row r="252" spans="4:11">
+    <row r="252" spans="3:11">
+      <c r="C252">
+        <v>1</v>
+      </c>
       <c r="D252" t="s">
         <v>12</v>
       </c>
@@ -16969,7 +17946,10 @@
         <v>897</v>
       </c>
     </row>
-    <row r="253" spans="4:11">
+    <row r="253" spans="3:11">
+      <c r="C253">
+        <v>1</v>
+      </c>
       <c r="D253" t="s">
         <v>12</v>
       </c>
@@ -16995,7 +17975,10 @@
         <v>899</v>
       </c>
     </row>
-    <row r="254" spans="4:11">
+    <row r="254" spans="3:11">
+      <c r="C254">
+        <v>1</v>
+      </c>
       <c r="D254" t="s">
         <v>12</v>
       </c>
@@ -17021,7 +18004,10 @@
         <v>901</v>
       </c>
     </row>
-    <row r="255" spans="4:11">
+    <row r="255" spans="3:11">
+      <c r="C255">
+        <v>1</v>
+      </c>
       <c r="D255" t="s">
         <v>12</v>
       </c>
@@ -17047,7 +18033,10 @@
         <v>904</v>
       </c>
     </row>
-    <row r="256" spans="4:11">
+    <row r="256" spans="3:11">
+      <c r="C256">
+        <v>1</v>
+      </c>
       <c r="D256" t="s">
         <v>12</v>
       </c>
@@ -17073,7 +18062,10 @@
         <v>908</v>
       </c>
     </row>
-    <row r="257" spans="4:11">
+    <row r="257" spans="3:11">
+      <c r="C257">
+        <v>1</v>
+      </c>
       <c r="D257" t="s">
         <v>12</v>
       </c>
@@ -17099,7 +18091,10 @@
         <v>910</v>
       </c>
     </row>
-    <row r="258" spans="4:11">
+    <row r="258" spans="3:11">
+      <c r="C258">
+        <v>1</v>
+      </c>
       <c r="D258" t="s">
         <v>12</v>
       </c>
@@ -17125,7 +18120,10 @@
         <v>912</v>
       </c>
     </row>
-    <row r="259" spans="4:11">
+    <row r="259" spans="3:11">
+      <c r="C259">
+        <v>1</v>
+      </c>
       <c r="D259" t="s">
         <v>12</v>
       </c>
@@ -17151,7 +18149,10 @@
         <v>914</v>
       </c>
     </row>
-    <row r="260" spans="4:11">
+    <row r="260" spans="3:11">
+      <c r="C260">
+        <v>1</v>
+      </c>
       <c r="D260" t="s">
         <v>12</v>
       </c>
@@ -17177,7 +18178,10 @@
         <v>916</v>
       </c>
     </row>
-    <row r="261" spans="4:11">
+    <row r="261" spans="3:11">
+      <c r="C261">
+        <v>1</v>
+      </c>
       <c r="D261" t="s">
         <v>12</v>
       </c>
@@ -17203,7 +18207,10 @@
         <v>918</v>
       </c>
     </row>
-    <row r="262" spans="4:11">
+    <row r="262" spans="3:11">
+      <c r="C262">
+        <v>1</v>
+      </c>
       <c r="D262" t="s">
         <v>12</v>
       </c>
@@ -17229,7 +18236,10 @@
         <v>920</v>
       </c>
     </row>
-    <row r="263" spans="4:11">
+    <row r="263" spans="3:11">
+      <c r="C263">
+        <v>1</v>
+      </c>
       <c r="D263" t="s">
         <v>12</v>
       </c>
@@ -17255,7 +18265,10 @@
         <v>922</v>
       </c>
     </row>
-    <row r="264" spans="4:11">
+    <row r="264" spans="3:11">
+      <c r="C264">
+        <v>1</v>
+      </c>
       <c r="D264" t="s">
         <v>12</v>
       </c>
@@ -17281,7 +18294,10 @@
         <v>926</v>
       </c>
     </row>
-    <row r="265" spans="4:11">
+    <row r="265" spans="3:11">
+      <c r="C265">
+        <v>1</v>
+      </c>
       <c r="D265" t="s">
         <v>12</v>
       </c>
@@ -17307,7 +18323,10 @@
         <v>930</v>
       </c>
     </row>
-    <row r="266" spans="4:11">
+    <row r="266" spans="3:11">
+      <c r="C266">
+        <v>1</v>
+      </c>
       <c r="D266" t="s">
         <v>12</v>
       </c>
@@ -17333,7 +18352,10 @@
         <v>934</v>
       </c>
     </row>
-    <row r="267" spans="4:11">
+    <row r="267" spans="3:11">
+      <c r="C267">
+        <v>1</v>
+      </c>
       <c r="D267" t="s">
         <v>12</v>
       </c>
@@ -17359,7 +18381,10 @@
         <v>938</v>
       </c>
     </row>
-    <row r="268" spans="4:11">
+    <row r="268" spans="3:11">
+      <c r="C268">
+        <v>1</v>
+      </c>
       <c r="D268" t="s">
         <v>12</v>
       </c>
@@ -17385,7 +18410,10 @@
         <v>942</v>
       </c>
     </row>
-    <row r="269" spans="4:11">
+    <row r="269" spans="3:11">
+      <c r="C269">
+        <v>1</v>
+      </c>
       <c r="D269" t="s">
         <v>12</v>
       </c>
@@ -17411,7 +18439,10 @@
         <v>946</v>
       </c>
     </row>
-    <row r="270" spans="4:11">
+    <row r="270" spans="3:11">
+      <c r="C270">
+        <v>1</v>
+      </c>
       <c r="D270" t="s">
         <v>12</v>
       </c>
@@ -17437,7 +18468,10 @@
         <v>950</v>
       </c>
     </row>
-    <row r="271" spans="4:11">
+    <row r="271" spans="3:11">
+      <c r="C271">
+        <v>1</v>
+      </c>
       <c r="D271" t="s">
         <v>12</v>
       </c>
@@ -17463,7 +18497,10 @@
         <v>954</v>
       </c>
     </row>
-    <row r="272" spans="4:11">
+    <row r="272" spans="3:11">
+      <c r="C272">
+        <v>1</v>
+      </c>
       <c r="D272" t="s">
         <v>12</v>
       </c>
@@ -17489,7 +18526,10 @@
         <v>958</v>
       </c>
     </row>
-    <row r="273" spans="4:11">
+    <row r="273" spans="3:11">
+      <c r="C273">
+        <v>1</v>
+      </c>
       <c r="D273" t="s">
         <v>12</v>
       </c>
@@ -17515,7 +18555,10 @@
         <v>962</v>
       </c>
     </row>
-    <row r="274" spans="4:11">
+    <row r="274" spans="3:11">
+      <c r="C274">
+        <v>1</v>
+      </c>
       <c r="D274" t="s">
         <v>12</v>
       </c>
@@ -17541,7 +18584,10 @@
         <v>966</v>
       </c>
     </row>
-    <row r="275" spans="4:11">
+    <row r="275" spans="3:11">
+      <c r="C275">
+        <v>1</v>
+      </c>
       <c r="D275" t="s">
         <v>12</v>
       </c>
@@ -17567,7 +18613,10 @@
         <v>970</v>
       </c>
     </row>
-    <row r="276" spans="4:11">
+    <row r="276" spans="3:11">
+      <c r="C276">
+        <v>1</v>
+      </c>
       <c r="D276" t="s">
         <v>12</v>
       </c>
@@ -17593,7 +18642,10 @@
         <v>974</v>
       </c>
     </row>
-    <row r="277" spans="4:11">
+    <row r="277" spans="3:11">
+      <c r="C277">
+        <v>1</v>
+      </c>
       <c r="D277" t="s">
         <v>12</v>
       </c>
@@ -17619,7 +18671,10 @@
         <v>978</v>
       </c>
     </row>
-    <row r="278" spans="4:11">
+    <row r="278" spans="3:11">
+      <c r="C278">
+        <v>1</v>
+      </c>
       <c r="D278" t="s">
         <v>12</v>
       </c>
@@ -17645,7 +18700,10 @@
         <v>982</v>
       </c>
     </row>
-    <row r="279" spans="4:11">
+    <row r="279" spans="3:11">
+      <c r="C279">
+        <v>1</v>
+      </c>
       <c r="D279" t="s">
         <v>12</v>
       </c>
@@ -17671,7 +18729,10 @@
         <v>984</v>
       </c>
     </row>
-    <row r="280" spans="4:11">
+    <row r="280" spans="3:11">
+      <c r="C280">
+        <v>1</v>
+      </c>
       <c r="D280" t="s">
         <v>12</v>
       </c>
@@ -17697,7 +18758,10 @@
         <v>986</v>
       </c>
     </row>
-    <row r="281" spans="4:11">
+    <row r="281" spans="3:11">
+      <c r="C281">
+        <v>1</v>
+      </c>
       <c r="D281" t="s">
         <v>12</v>
       </c>
@@ -17723,7 +18787,10 @@
         <v>990</v>
       </c>
     </row>
-    <row r="282" spans="4:11">
+    <row r="282" spans="3:11">
+      <c r="C282">
+        <v>1</v>
+      </c>
       <c r="D282" t="s">
         <v>12</v>
       </c>
@@ -17749,7 +18816,10 @@
         <v>994</v>
       </c>
     </row>
-    <row r="283" spans="4:11">
+    <row r="283" spans="3:11">
+      <c r="C283">
+        <v>1</v>
+      </c>
       <c r="D283" t="s">
         <v>12</v>
       </c>
@@ -17775,7 +18845,10 @@
         <v>998</v>
       </c>
     </row>
-    <row r="284" spans="4:11">
+    <row r="284" spans="3:11">
+      <c r="C284">
+        <v>1</v>
+      </c>
       <c r="D284" t="s">
         <v>12</v>
       </c>
@@ -17801,7 +18874,10 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="285" spans="4:11">
+    <row r="285" spans="3:11">
+      <c r="C285">
+        <v>1</v>
+      </c>
       <c r="D285" t="s">
         <v>12</v>
       </c>
@@ -17827,7 +18903,10 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="286" spans="4:11">
+    <row r="286" spans="3:11">
+      <c r="C286">
+        <v>1</v>
+      </c>
       <c r="D286" t="s">
         <v>12</v>
       </c>
@@ -17853,7 +18932,10 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="287" spans="4:11">
+    <row r="287" spans="3:11">
+      <c r="C287">
+        <v>1</v>
+      </c>
       <c r="D287" t="s">
         <v>12</v>
       </c>
@@ -17879,7 +18961,10 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="288" spans="4:11">
+    <row r="288" spans="3:11">
+      <c r="C288">
+        <v>1</v>
+      </c>
       <c r="D288" t="s">
         <v>12</v>
       </c>
@@ -17905,7 +18990,10 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="289" spans="4:11">
+    <row r="289" spans="3:11">
+      <c r="C289">
+        <v>1</v>
+      </c>
       <c r="D289" t="s">
         <v>12</v>
       </c>
@@ -17931,7 +19019,10 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="290" spans="4:11">
+    <row r="290" spans="3:11">
+      <c r="C290">
+        <v>1</v>
+      </c>
       <c r="D290" t="s">
         <v>12</v>
       </c>
@@ -17957,7 +19048,10 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="291" spans="4:11">
+    <row r="291" spans="3:11">
+      <c r="C291">
+        <v>1</v>
+      </c>
       <c r="D291" t="s">
         <v>12</v>
       </c>
@@ -17983,7 +19077,10 @@
         <v>1023</v>
       </c>
     </row>
-    <row r="292" spans="4:11">
+    <row r="292" spans="3:11">
+      <c r="C292">
+        <v>1</v>
+      </c>
       <c r="D292" t="s">
         <v>12</v>
       </c>
@@ -18009,7 +19106,10 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="293" spans="4:11">
+    <row r="293" spans="3:11">
+      <c r="C293">
+        <v>1</v>
+      </c>
       <c r="D293" t="s">
         <v>12</v>
       </c>
@@ -18035,7 +19135,10 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="294" spans="4:11">
+    <row r="294" spans="3:11">
+      <c r="C294">
+        <v>1</v>
+      </c>
       <c r="D294" t="s">
         <v>12</v>
       </c>
@@ -18061,7 +19164,10 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="295" spans="4:11">
+    <row r="295" spans="3:11">
+      <c r="C295">
+        <v>1</v>
+      </c>
       <c r="D295" t="s">
         <v>12</v>
       </c>
@@ -18087,7 +19193,10 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="296" spans="4:11">
+    <row r="296" spans="3:11">
+      <c r="C296">
+        <v>1</v>
+      </c>
       <c r="D296" t="s">
         <v>12</v>
       </c>
@@ -18113,7 +19222,10 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="297" spans="4:11">
+    <row r="297" spans="3:11">
+      <c r="C297">
+        <v>1</v>
+      </c>
       <c r="D297" t="s">
         <v>12</v>
       </c>
@@ -18139,7 +19251,10 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="298" spans="4:11">
+    <row r="298" spans="3:11">
+      <c r="C298">
+        <v>1</v>
+      </c>
       <c r="D298" t="s">
         <v>12</v>
       </c>
@@ -18165,7 +19280,10 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="299" spans="4:11">
+    <row r="299" spans="3:11">
+      <c r="C299">
+        <v>1</v>
+      </c>
       <c r="D299" t="s">
         <v>12</v>
       </c>
@@ -18191,7 +19309,10 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="300" spans="4:11">
+    <row r="300" spans="3:11">
+      <c r="C300">
+        <v>1</v>
+      </c>
       <c r="D300" t="s">
         <v>12</v>
       </c>
@@ -18217,7 +19338,10 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="301" spans="4:11">
+    <row r="301" spans="3:11">
+      <c r="C301">
+        <v>1</v>
+      </c>
       <c r="D301" t="s">
         <v>12</v>
       </c>
@@ -18243,7 +19367,10 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="302" spans="4:11">
+    <row r="302" spans="3:11">
+      <c r="C302">
+        <v>1</v>
+      </c>
       <c r="D302" t="s">
         <v>12</v>
       </c>
@@ -18269,7 +19396,10 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="303" spans="4:11">
+    <row r="303" spans="3:11">
+      <c r="C303">
+        <v>1</v>
+      </c>
       <c r="D303" t="s">
         <v>12</v>
       </c>
@@ -18295,7 +19425,10 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="304" spans="4:11">
+    <row r="304" spans="3:11">
+      <c r="C304">
+        <v>1</v>
+      </c>
       <c r="D304" t="s">
         <v>12</v>
       </c>
@@ -18321,7 +19454,10 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="305" spans="4:11">
+    <row r="305" spans="3:11">
+      <c r="C305">
+        <v>1</v>
+      </c>
       <c r="D305" t="s">
         <v>12</v>
       </c>
@@ -18347,7 +19483,10 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="306" spans="4:11">
+    <row r="306" spans="3:11">
+      <c r="C306">
+        <v>1</v>
+      </c>
       <c r="D306" t="s">
         <v>12</v>
       </c>
@@ -18373,7 +19512,10 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="307" spans="4:11">
+    <row r="307" spans="3:11">
+      <c r="C307">
+        <v>1</v>
+      </c>
       <c r="D307" t="s">
         <v>12</v>
       </c>
@@ -18399,7 +19541,10 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="308" spans="4:11">
+    <row r="308" spans="3:11">
+      <c r="C308">
+        <v>1</v>
+      </c>
       <c r="D308" t="s">
         <v>12</v>
       </c>
@@ -18425,7 +19570,10 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="309" spans="4:11">
+    <row r="309" spans="3:11">
+      <c r="C309">
+        <v>1</v>
+      </c>
       <c r="D309" t="s">
         <v>12</v>
       </c>
@@ -18451,7 +19599,10 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="310" spans="4:11">
+    <row r="310" spans="3:11">
+      <c r="C310">
+        <v>1</v>
+      </c>
       <c r="D310" t="s">
         <v>12</v>
       </c>
@@ -18477,7 +19628,10 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="311" spans="4:11">
+    <row r="311" spans="3:11">
+      <c r="C311">
+        <v>1</v>
+      </c>
       <c r="D311" t="s">
         <v>12</v>
       </c>
@@ -18503,7 +19657,10 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="312" spans="4:11">
+    <row r="312" spans="3:11">
+      <c r="C312">
+        <v>1</v>
+      </c>
       <c r="D312" t="s">
         <v>12</v>
       </c>
@@ -18529,7 +19686,10 @@
         <v>1093</v>
       </c>
     </row>
-    <row r="313" spans="4:11">
+    <row r="313" spans="3:11">
+      <c r="C313">
+        <v>1</v>
+      </c>
       <c r="D313" t="s">
         <v>12</v>
       </c>
@@ -18555,7 +19715,10 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="314" spans="4:11">
+    <row r="314" spans="3:11">
+      <c r="C314">
+        <v>1</v>
+      </c>
       <c r="D314" t="s">
         <v>12</v>
       </c>
@@ -18581,7 +19744,10 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="315" spans="4:11">
+    <row r="315" spans="3:11">
+      <c r="C315">
+        <v>1</v>
+      </c>
       <c r="D315" t="s">
         <v>12</v>
       </c>
@@ -18607,7 +19773,10 @@
         <v>1102</v>
       </c>
     </row>
-    <row r="316" spans="4:11">
+    <row r="316" spans="3:11">
+      <c r="C316">
+        <v>1</v>
+      </c>
       <c r="D316" t="s">
         <v>12</v>
       </c>
@@ -18633,7 +19802,10 @@
         <v>1105</v>
       </c>
     </row>
-    <row r="317" spans="4:11">
+    <row r="317" spans="3:11">
+      <c r="C317">
+        <v>1</v>
+      </c>
       <c r="D317" t="s">
         <v>12</v>
       </c>
@@ -18659,7 +19831,10 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="318" spans="4:11">
+    <row r="318" spans="3:11">
+      <c r="C318">
+        <v>1</v>
+      </c>
       <c r="D318" t="s">
         <v>12</v>
       </c>
@@ -18685,7 +19860,10 @@
         <v>1112</v>
       </c>
     </row>
-    <row r="319" spans="4:11">
+    <row r="319" spans="3:11">
+      <c r="C319">
+        <v>1</v>
+      </c>
       <c r="D319" t="s">
         <v>12</v>
       </c>
@@ -18711,7 +19889,10 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="320" spans="4:11">
+    <row r="320" spans="3:11">
+      <c r="C320">
+        <v>1</v>
+      </c>
       <c r="D320" t="s">
         <v>12</v>
       </c>
@@ -18737,7 +19918,10 @@
         <v>1118</v>
       </c>
     </row>
-    <row r="321" spans="4:11">
+    <row r="321" spans="3:11">
+      <c r="C321">
+        <v>1</v>
+      </c>
       <c r="D321" t="s">
         <v>12</v>
       </c>
@@ -18763,7 +19947,10 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="322" spans="4:11">
+    <row r="322" spans="3:11">
+      <c r="C322">
+        <v>1</v>
+      </c>
       <c r="D322" t="s">
         <v>12</v>
       </c>
@@ -18789,7 +19976,10 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="323" spans="4:11">
+    <row r="323" spans="3:11">
+      <c r="C323">
+        <v>1</v>
+      </c>
       <c r="D323" t="s">
         <v>12</v>
       </c>
@@ -18815,7 +20005,10 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="324" spans="4:11">
+    <row r="324" spans="3:11">
+      <c r="C324">
+        <v>1</v>
+      </c>
       <c r="D324" t="s">
         <v>12</v>
       </c>
@@ -18841,7 +20034,10 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="325" spans="4:11">
+    <row r="325" spans="3:11">
+      <c r="C325">
+        <v>1</v>
+      </c>
       <c r="D325" t="s">
         <v>12</v>
       </c>
@@ -18867,7 +20063,10 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="326" spans="4:11">
+    <row r="326" spans="3:11">
+      <c r="C326">
+        <v>1</v>
+      </c>
       <c r="D326" t="s">
         <v>12</v>
       </c>
@@ -18893,7 +20092,10 @@
         <v>1138</v>
       </c>
     </row>
-    <row r="327" spans="4:11">
+    <row r="327" spans="3:11">
+      <c r="C327">
+        <v>1</v>
+      </c>
       <c r="D327" t="s">
         <v>12</v>
       </c>
@@ -18919,7 +20121,10 @@
         <v>1141</v>
       </c>
     </row>
-    <row r="328" spans="4:11">
+    <row r="328" spans="3:11">
+      <c r="C328">
+        <v>1</v>
+      </c>
       <c r="D328" t="s">
         <v>12</v>
       </c>
@@ -18945,7 +20150,10 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="329" spans="4:11">
+    <row r="329" spans="3:11">
+      <c r="C329">
+        <v>1</v>
+      </c>
       <c r="D329" t="s">
         <v>12</v>
       </c>
@@ -18971,7 +20179,10 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="330" spans="4:11">
+    <row r="330" spans="3:11">
+      <c r="C330">
+        <v>1</v>
+      </c>
       <c r="D330" t="s">
         <v>12</v>
       </c>
@@ -18997,7 +20208,10 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="331" spans="4:11">
+    <row r="331" spans="3:11">
+      <c r="C331">
+        <v>1</v>
+      </c>
       <c r="D331" t="s">
         <v>12</v>
       </c>
@@ -19023,7 +20237,10 @@
         <v>1155</v>
       </c>
     </row>
-    <row r="332" spans="4:11">
+    <row r="332" spans="3:11">
+      <c r="C332">
+        <v>1</v>
+      </c>
       <c r="D332" t="s">
         <v>12</v>
       </c>
@@ -19049,7 +20266,10 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="333" spans="4:11">
+    <row r="333" spans="3:11">
+      <c r="C333">
+        <v>1</v>
+      </c>
       <c r="D333" t="s">
         <v>12</v>
       </c>
@@ -19075,7 +20295,10 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="334" spans="4:11">
+    <row r="334" spans="3:11">
+      <c r="C334">
+        <v>1</v>
+      </c>
       <c r="D334" t="s">
         <v>12</v>
       </c>
@@ -19101,7 +20324,10 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="335" spans="4:11">
+    <row r="335" spans="3:11">
+      <c r="C335">
+        <v>1</v>
+      </c>
       <c r="D335" t="s">
         <v>12</v>
       </c>
@@ -19127,7 +20353,10 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="336" spans="4:11">
+    <row r="336" spans="3:11">
+      <c r="C336">
+        <v>1</v>
+      </c>
       <c r="D336" t="s">
         <v>12</v>
       </c>
@@ -19153,7 +20382,10 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="337" spans="4:11">
+    <row r="337" spans="3:11">
+      <c r="C337">
+        <v>1</v>
+      </c>
       <c r="D337" t="s">
         <v>12</v>
       </c>
@@ -19179,7 +20411,10 @@
         <v>1179</v>
       </c>
     </row>
-    <row r="338" spans="4:11">
+    <row r="338" spans="3:11">
+      <c r="C338">
+        <v>1</v>
+      </c>
       <c r="D338" t="s">
         <v>12</v>
       </c>
@@ -19205,7 +20440,10 @@
         <v>1183</v>
       </c>
     </row>
-    <row r="339" spans="4:11">
+    <row r="339" spans="3:11">
+      <c r="C339">
+        <v>1</v>
+      </c>
       <c r="D339" t="s">
         <v>12</v>
       </c>
@@ -19231,7 +20469,10 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="340" spans="4:11">
+    <row r="340" spans="3:11">
+      <c r="C340">
+        <v>1</v>
+      </c>
       <c r="D340" t="s">
         <v>12</v>
       </c>
@@ -19257,7 +20498,10 @@
         <v>1191</v>
       </c>
     </row>
-    <row r="341" spans="4:11">
+    <row r="341" spans="3:11">
+      <c r="C341">
+        <v>1</v>
+      </c>
       <c r="D341" t="s">
         <v>12</v>
       </c>
@@ -19283,7 +20527,10 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="342" spans="4:11">
+    <row r="342" spans="3:11">
+      <c r="C342">
+        <v>1</v>
+      </c>
       <c r="D342" t="s">
         <v>12</v>
       </c>
@@ -19309,7 +20556,10 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="343" spans="4:11">
+    <row r="343" spans="3:11">
+      <c r="C343">
+        <v>1</v>
+      </c>
       <c r="D343" t="s">
         <v>12</v>
       </c>
@@ -19335,7 +20585,10 @@
         <v>1203</v>
       </c>
     </row>
-    <row r="344" spans="4:11">
+    <row r="344" spans="3:11">
+      <c r="C344">
+        <v>1</v>
+      </c>
       <c r="D344" t="s">
         <v>12</v>
       </c>
@@ -19361,7 +20614,10 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="345" spans="4:11">
+    <row r="345" spans="3:11">
+      <c r="C345">
+        <v>1</v>
+      </c>
       <c r="D345" t="s">
         <v>12</v>
       </c>
@@ -19387,7 +20643,10 @@
         <v>1211</v>
       </c>
     </row>
-    <row r="346" spans="4:11">
+    <row r="346" spans="3:11">
+      <c r="C346">
+        <v>1</v>
+      </c>
       <c r="D346" t="s">
         <v>12</v>
       </c>
@@ -19413,7 +20672,10 @@
         <v>1215</v>
       </c>
     </row>
-    <row r="347" spans="4:11">
+    <row r="347" spans="3:11">
+      <c r="C347">
+        <v>1</v>
+      </c>
       <c r="D347" t="s">
         <v>12</v>
       </c>
@@ -19439,7 +20701,10 @@
         <v>1219</v>
       </c>
     </row>
-    <row r="348" spans="4:11">
+    <row r="348" spans="3:11">
+      <c r="C348">
+        <v>1</v>
+      </c>
       <c r="D348" t="s">
         <v>12</v>
       </c>
@@ -19465,7 +20730,10 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="349" spans="4:11">
+    <row r="349" spans="3:11">
+      <c r="C349">
+        <v>1</v>
+      </c>
       <c r="D349" t="s">
         <v>12</v>
       </c>
@@ -19491,7 +20759,10 @@
         <v>1227</v>
       </c>
     </row>
-    <row r="350" spans="4:11">
+    <row r="350" spans="3:11">
+      <c r="C350">
+        <v>1</v>
+      </c>
       <c r="D350" t="s">
         <v>12</v>
       </c>
@@ -19517,7 +20788,10 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="351" spans="4:11">
+    <row r="351" spans="3:11">
+      <c r="C351">
+        <v>1</v>
+      </c>
       <c r="D351" t="s">
         <v>12</v>
       </c>
@@ -19543,7 +20817,10 @@
         <v>1235</v>
       </c>
     </row>
-    <row r="352" spans="4:11">
+    <row r="352" spans="3:11">
+      <c r="C352">
+        <v>1</v>
+      </c>
       <c r="D352" t="s">
         <v>12</v>
       </c>
@@ -19569,7 +20846,10 @@
         <v>1239</v>
       </c>
     </row>
-    <row r="353" spans="4:11">
+    <row r="353" spans="3:11">
+      <c r="C353">
+        <v>1</v>
+      </c>
       <c r="D353" t="s">
         <v>12</v>
       </c>
@@ -19595,7 +20875,10 @@
         <v>1243</v>
       </c>
     </row>
-    <row r="354" spans="4:11">
+    <row r="354" spans="3:11">
+      <c r="C354">
+        <v>1</v>
+      </c>
       <c r="D354" t="s">
         <v>12</v>
       </c>
@@ -19621,7 +20904,10 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="355" spans="4:11">
+    <row r="355" spans="3:11">
+      <c r="C355">
+        <v>1</v>
+      </c>
       <c r="D355" t="s">
         <v>12</v>
       </c>
@@ -19647,7 +20933,10 @@
         <v>1251</v>
       </c>
     </row>
-    <row r="356" spans="4:11">
+    <row r="356" spans="3:11">
+      <c r="C356">
+        <v>1</v>
+      </c>
       <c r="D356" t="s">
         <v>12</v>
       </c>
@@ -19673,7 +20962,10 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="357" spans="4:11">
+    <row r="357" spans="3:11">
+      <c r="C357">
+        <v>1</v>
+      </c>
       <c r="D357" t="s">
         <v>12</v>
       </c>
@@ -19699,7 +20991,10 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="358" spans="4:11">
+    <row r="358" spans="3:11">
+      <c r="C358">
+        <v>1</v>
+      </c>
       <c r="D358" t="s">
         <v>12</v>
       </c>
@@ -19725,7 +21020,10 @@
         <v>1263</v>
       </c>
     </row>
-    <row r="359" spans="4:11">
+    <row r="359" spans="3:11">
+      <c r="C359">
+        <v>1</v>
+      </c>
       <c r="D359" t="s">
         <v>12</v>
       </c>
@@ -19751,7 +21049,10 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="360" spans="4:11">
+    <row r="360" spans="3:11">
+      <c r="C360">
+        <v>1</v>
+      </c>
       <c r="D360" t="s">
         <v>12</v>
       </c>
@@ -19777,7 +21078,10 @@
         <v>1271</v>
       </c>
     </row>
-    <row r="361" spans="4:11">
+    <row r="361" spans="3:11">
+      <c r="C361">
+        <v>1</v>
+      </c>
       <c r="D361" t="s">
         <v>12</v>
       </c>
@@ -19803,7 +21107,10 @@
         <v>1275</v>
       </c>
     </row>
-    <row r="362" spans="4:11">
+    <row r="362" spans="3:11">
+      <c r="C362">
+        <v>1</v>
+      </c>
       <c r="D362" t="s">
         <v>12</v>
       </c>
@@ -19829,7 +21136,10 @@
         <v>1279</v>
       </c>
     </row>
-    <row r="363" spans="4:11">
+    <row r="363" spans="3:11">
+      <c r="C363">
+        <v>1</v>
+      </c>
       <c r="D363" t="s">
         <v>12</v>
       </c>
@@ -19855,7 +21165,10 @@
         <v>1283</v>
       </c>
     </row>
-    <row r="364" spans="4:11">
+    <row r="364" spans="3:11">
+      <c r="C364">
+        <v>1</v>
+      </c>
       <c r="D364" t="s">
         <v>12</v>
       </c>
@@ -19881,7 +21194,10 @@
         <v>1287</v>
       </c>
     </row>
-    <row r="365" spans="4:11">
+    <row r="365" spans="3:11">
+      <c r="C365">
+        <v>1</v>
+      </c>
       <c r="D365" t="s">
         <v>12</v>
       </c>
@@ -19907,7 +21223,10 @@
         <v>1291</v>
       </c>
     </row>
-    <row r="366" spans="4:11">
+    <row r="366" spans="3:11">
+      <c r="C366">
+        <v>1</v>
+      </c>
       <c r="D366" t="s">
         <v>12</v>
       </c>
@@ -19933,7 +21252,10 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="367" spans="4:11">
+    <row r="367" spans="3:11">
+      <c r="C367">
+        <v>1</v>
+      </c>
       <c r="D367" t="s">
         <v>12</v>
       </c>
@@ -19959,7 +21281,10 @@
         <v>1299</v>
       </c>
     </row>
-    <row r="368" spans="4:11">
+    <row r="368" spans="3:11">
+      <c r="C368">
+        <v>1</v>
+      </c>
       <c r="D368" t="s">
         <v>12</v>
       </c>
@@ -19985,7 +21310,10 @@
         <v>1303</v>
       </c>
     </row>
-    <row r="369" spans="4:11">
+    <row r="369" spans="3:11">
+      <c r="C369">
+        <v>1</v>
+      </c>
       <c r="D369" t="s">
         <v>12</v>
       </c>
@@ -20011,7 +21339,10 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="370" spans="4:11">
+    <row r="370" spans="3:11">
+      <c r="C370">
+        <v>1</v>
+      </c>
       <c r="D370" t="s">
         <v>12</v>
       </c>
@@ -20037,7 +21368,10 @@
         <v>1311</v>
       </c>
     </row>
-    <row r="371" spans="4:11">
+    <row r="371" spans="3:11">
+      <c r="C371">
+        <v>1</v>
+      </c>
       <c r="D371" t="s">
         <v>12</v>
       </c>
@@ -20063,7 +21397,10 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="372" spans="4:11">
+    <row r="372" spans="3:11">
+      <c r="C372">
+        <v>1</v>
+      </c>
       <c r="D372" t="s">
         <v>12</v>
       </c>
@@ -20089,7 +21426,10 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="373" spans="4:11">
+    <row r="373" spans="3:11">
+      <c r="C373">
+        <v>1</v>
+      </c>
       <c r="D373" t="s">
         <v>12</v>
       </c>
@@ -20115,7 +21455,10 @@
         <v>1323</v>
       </c>
     </row>
-    <row r="374" spans="4:11">
+    <row r="374" spans="3:11">
+      <c r="C374">
+        <v>1</v>
+      </c>
       <c r="D374" t="s">
         <v>12</v>
       </c>
@@ -20141,7 +21484,7 @@
         <v>1327</v>
       </c>
     </row>
-    <row r="375" spans="4:11">
+    <row r="375" spans="3:11">
       <c r="D375" t="s">
         <v>12</v>
       </c>
@@ -20167,7 +21510,7 @@
         <v>1331</v>
       </c>
     </row>
-    <row r="376" spans="4:11">
+    <row r="376" spans="3:11">
       <c r="D376" t="s">
         <v>12</v>
       </c>
@@ -20193,7 +21536,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="377" spans="4:11">
+    <row r="377" spans="3:11">
       <c r="D377" t="s">
         <v>12</v>
       </c>
@@ -20219,7 +21562,7 @@
         <v>1339</v>
       </c>
     </row>
-    <row r="378" spans="4:11">
+    <row r="378" spans="3:11">
       <c r="D378" t="s">
         <v>12</v>
       </c>
@@ -20245,7 +21588,7 @@
         <v>1343</v>
       </c>
     </row>
-    <row r="379" spans="4:11">
+    <row r="379" spans="3:11">
       <c r="D379" t="s">
         <v>12</v>
       </c>
@@ -20271,7 +21614,7 @@
         <v>1347</v>
       </c>
     </row>
-    <row r="380" spans="4:11">
+    <row r="380" spans="3:11">
       <c r="D380" t="s">
         <v>12</v>
       </c>
@@ -20297,7 +21640,7 @@
         <v>1351</v>
       </c>
     </row>
-    <row r="381" spans="4:11">
+    <row r="381" spans="3:11">
       <c r="D381" t="s">
         <v>12</v>
       </c>
@@ -20323,7 +21666,7 @@
         <v>1355</v>
       </c>
     </row>
-    <row r="382" spans="4:11">
+    <row r="382" spans="3:11">
       <c r="D382" t="s">
         <v>12</v>
       </c>
@@ -20349,7 +21692,7 @@
         <v>1359</v>
       </c>
     </row>
-    <row r="383" spans="4:11">
+    <row r="383" spans="3:11">
       <c r="D383" t="s">
         <v>12</v>
       </c>
@@ -20375,7 +21718,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="384" spans="4:11">
+    <row r="384" spans="3:11">
       <c r="D384" t="s">
         <v>12</v>
       </c>
@@ -22314,6 +23657,9 @@
       <c r="B456">
         <v>1</v>
       </c>
+      <c r="C456">
+        <v>1</v>
+      </c>
       <c r="D456" t="s">
         <v>1508</v>
       </c>
@@ -22343,6 +23689,9 @@
       <c r="B457">
         <v>1</v>
       </c>
+      <c r="C457">
+        <v>1</v>
+      </c>
       <c r="D457" t="s">
         <v>1508</v>
       </c>
@@ -22372,6 +23721,9 @@
       <c r="B458">
         <v>1</v>
       </c>
+      <c r="C458">
+        <v>1</v>
+      </c>
       <c r="D458" t="s">
         <v>1508</v>
       </c>
@@ -22401,6 +23753,9 @@
       <c r="B459">
         <v>1</v>
       </c>
+      <c r="C459">
+        <v>1</v>
+      </c>
       <c r="D459" t="s">
         <v>1508</v>
       </c>
@@ -22430,6 +23785,9 @@
       <c r="B460">
         <v>1</v>
       </c>
+      <c r="C460">
+        <v>1</v>
+      </c>
       <c r="D460" t="s">
         <v>1508</v>
       </c>
@@ -22459,6 +23817,9 @@
       <c r="B461">
         <v>1</v>
       </c>
+      <c r="C461">
+        <v>1</v>
+      </c>
       <c r="D461" t="s">
         <v>1508</v>
       </c>
@@ -22488,6 +23849,9 @@
       <c r="B462">
         <v>1</v>
       </c>
+      <c r="C462">
+        <v>1</v>
+      </c>
       <c r="D462" t="s">
         <v>1508</v>
       </c>
@@ -22517,6 +23881,9 @@
       <c r="B463">
         <v>1</v>
       </c>
+      <c r="C463">
+        <v>1</v>
+      </c>
       <c r="D463" t="s">
         <v>1508</v>
       </c>
@@ -22546,6 +23913,9 @@
       <c r="B464">
         <v>1</v>
       </c>
+      <c r="C464">
+        <v>1</v>
+      </c>
       <c r="D464" t="s">
         <v>1508</v>
       </c>
@@ -22575,6 +23945,9 @@
       <c r="B465">
         <v>1</v>
       </c>
+      <c r="C465">
+        <v>1</v>
+      </c>
       <c r="D465" t="s">
         <v>1508</v>
       </c>
@@ -22604,6 +23977,9 @@
       <c r="B466">
         <v>1</v>
       </c>
+      <c r="C466">
+        <v>1</v>
+      </c>
       <c r="D466" t="s">
         <v>1508</v>
       </c>
@@ -22631,6 +24007,9 @@
     </row>
     <row r="467" spans="2:11">
       <c r="B467">
+        <v>1</v>
+      </c>
+      <c r="C467">
         <v>1</v>
       </c>
       <c r="D467" t="s">
@@ -22971,6 +24350,9 @@
       </c>
     </row>
     <row r="480" spans="2:11">
+      <c r="C480">
+        <v>1</v>
+      </c>
       <c r="D480" t="s">
         <v>1508</v>
       </c>
@@ -22996,7 +24378,10 @@
         <v>1759</v>
       </c>
     </row>
-    <row r="481" spans="4:11">
+    <row r="481" spans="3:11">
+      <c r="C481">
+        <v>1</v>
+      </c>
       <c r="D481" t="s">
         <v>1508</v>
       </c>
@@ -23022,7 +24407,10 @@
         <v>1763</v>
       </c>
     </row>
-    <row r="482" spans="4:11">
+    <row r="482" spans="3:11">
+      <c r="C482">
+        <v>1</v>
+      </c>
       <c r="D482" t="s">
         <v>1508</v>
       </c>
@@ -23048,7 +24436,10 @@
         <v>1767</v>
       </c>
     </row>
-    <row r="483" spans="4:11">
+    <row r="483" spans="3:11">
+      <c r="C483">
+        <v>1</v>
+      </c>
       <c r="D483" t="s">
         <v>1508</v>
       </c>
@@ -23074,7 +24465,10 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="484" spans="4:11">
+    <row r="484" spans="3:11">
+      <c r="C484">
+        <v>1</v>
+      </c>
       <c r="D484" t="s">
         <v>1508</v>
       </c>
@@ -23100,7 +24494,10 @@
         <v>1775</v>
       </c>
     </row>
-    <row r="485" spans="4:11">
+    <row r="485" spans="3:11">
+      <c r="C485">
+        <v>1</v>
+      </c>
       <c r="D485" t="s">
         <v>1508</v>
       </c>
@@ -23126,7 +24523,10 @@
         <v>1779</v>
       </c>
     </row>
-    <row r="486" spans="4:11">
+    <row r="486" spans="3:11">
+      <c r="C486">
+        <v>1</v>
+      </c>
       <c r="D486" t="s">
         <v>1508</v>
       </c>
@@ -23152,7 +24552,10 @@
         <v>1783</v>
       </c>
     </row>
-    <row r="487" spans="4:11">
+    <row r="487" spans="3:11">
+      <c r="C487">
+        <v>1</v>
+      </c>
       <c r="D487" t="s">
         <v>1508</v>
       </c>
@@ -23178,7 +24581,10 @@
         <v>1787</v>
       </c>
     </row>
-    <row r="488" spans="4:11">
+    <row r="488" spans="3:11">
+      <c r="C488">
+        <v>1</v>
+      </c>
       <c r="D488" t="s">
         <v>1508</v>
       </c>
@@ -23204,7 +24610,10 @@
         <v>1792</v>
       </c>
     </row>
-    <row r="489" spans="4:11">
+    <row r="489" spans="3:11">
+      <c r="C489">
+        <v>1</v>
+      </c>
       <c r="D489" t="s">
         <v>1508</v>
       </c>
@@ -23230,7 +24639,10 @@
         <v>1796</v>
       </c>
     </row>
-    <row r="490" spans="4:11">
+    <row r="490" spans="3:11">
+      <c r="C490">
+        <v>1</v>
+      </c>
       <c r="D490" t="s">
         <v>1508</v>
       </c>
@@ -23256,7 +24668,10 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="491" spans="4:11">
+    <row r="491" spans="3:11">
+      <c r="C491">
+        <v>1</v>
+      </c>
       <c r="D491" t="s">
         <v>1508</v>
       </c>
@@ -23282,7 +24697,10 @@
         <v>1804</v>
       </c>
     </row>
-    <row r="492" spans="4:11">
+    <row r="492" spans="3:11">
+      <c r="C492">
+        <v>1</v>
+      </c>
       <c r="D492" t="s">
         <v>1508</v>
       </c>
@@ -23308,7 +24726,7 @@
         <v>1808</v>
       </c>
     </row>
-    <row r="493" spans="4:11">
+    <row r="493" spans="3:11">
       <c r="D493" t="s">
         <v>1508</v>
       </c>
@@ -23334,7 +24752,7 @@
         <v>1814</v>
       </c>
     </row>
-    <row r="494" spans="4:11">
+    <row r="494" spans="3:11">
       <c r="D494" t="s">
         <v>1508</v>
       </c>
@@ -23360,7 +24778,7 @@
         <v>1818</v>
       </c>
     </row>
-    <row r="495" spans="4:11">
+    <row r="495" spans="3:11">
       <c r="D495" t="s">
         <v>1508</v>
       </c>
@@ -23386,7 +24804,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="496" spans="4:11">
+    <row r="496" spans="3:11">
       <c r="D496" t="s">
         <v>1508</v>
       </c>
@@ -23412,7 +24830,7 @@
         <v>1826</v>
       </c>
     </row>
-    <row r="497" spans="4:11">
+    <row r="497" spans="3:11">
       <c r="D497" t="s">
         <v>1508</v>
       </c>
@@ -23438,7 +24856,7 @@
         <v>1830</v>
       </c>
     </row>
-    <row r="498" spans="4:11">
+    <row r="498" spans="3:11">
       <c r="D498" t="s">
         <v>1508</v>
       </c>
@@ -23464,7 +24882,7 @@
         <v>1834</v>
       </c>
     </row>
-    <row r="499" spans="4:11">
+    <row r="499" spans="3:11">
       <c r="D499" t="s">
         <v>1508</v>
       </c>
@@ -23490,7 +24908,7 @@
         <v>1838</v>
       </c>
     </row>
-    <row r="500" spans="4:11">
+    <row r="500" spans="3:11">
       <c r="D500" t="s">
         <v>1508</v>
       </c>
@@ -23516,7 +24934,7 @@
         <v>1842</v>
       </c>
     </row>
-    <row r="501" spans="4:11">
+    <row r="501" spans="3:11">
       <c r="D501" t="s">
         <v>1508</v>
       </c>
@@ -23542,7 +24960,10 @@
         <v>1846</v>
       </c>
     </row>
-    <row r="502" spans="4:11">
+    <row r="502" spans="3:11">
+      <c r="C502">
+        <v>1</v>
+      </c>
       <c r="D502" t="s">
         <v>1508</v>
       </c>
@@ -23568,7 +24989,10 @@
         <v>1850</v>
       </c>
     </row>
-    <row r="503" spans="4:11">
+    <row r="503" spans="3:11">
+      <c r="C503">
+        <v>1</v>
+      </c>
       <c r="D503" t="s">
         <v>1508</v>
       </c>
@@ -23594,7 +25018,10 @@
         <v>1854</v>
       </c>
     </row>
-    <row r="504" spans="4:11">
+    <row r="504" spans="3:11">
+      <c r="C504">
+        <v>1</v>
+      </c>
       <c r="D504" t="s">
         <v>1508</v>
       </c>
@@ -23620,7 +25047,10 @@
         <v>1858</v>
       </c>
     </row>
-    <row r="505" spans="4:11">
+    <row r="505" spans="3:11">
+      <c r="C505">
+        <v>1</v>
+      </c>
       <c r="D505" t="s">
         <v>1508</v>
       </c>
@@ -23646,7 +25076,10 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="506" spans="4:11">
+    <row r="506" spans="3:11">
+      <c r="C506">
+        <v>1</v>
+      </c>
       <c r="D506" t="s">
         <v>1508</v>
       </c>
@@ -23672,7 +25105,10 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="507" spans="4:11">
+    <row r="507" spans="3:11">
+      <c r="C507">
+        <v>1</v>
+      </c>
       <c r="D507" t="s">
         <v>1508</v>
       </c>
@@ -23698,7 +25134,10 @@
         <v>1870</v>
       </c>
     </row>
-    <row r="508" spans="4:11">
+    <row r="508" spans="3:11">
+      <c r="C508">
+        <v>1</v>
+      </c>
       <c r="D508" t="s">
         <v>1508</v>
       </c>
@@ -23724,7 +25163,10 @@
         <v>1874</v>
       </c>
     </row>
-    <row r="509" spans="4:11">
+    <row r="509" spans="3:11">
+      <c r="C509">
+        <v>1</v>
+      </c>
       <c r="D509" t="s">
         <v>1508</v>
       </c>
@@ -23750,7 +25192,10 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="510" spans="4:11">
+    <row r="510" spans="3:11">
+      <c r="C510">
+        <v>1</v>
+      </c>
       <c r="D510" t="s">
         <v>1508</v>
       </c>
@@ -23776,7 +25221,10 @@
         <v>1882</v>
       </c>
     </row>
-    <row r="511" spans="4:11">
+    <row r="511" spans="3:11">
+      <c r="C511">
+        <v>1</v>
+      </c>
       <c r="D511" t="s">
         <v>1508</v>
       </c>
@@ -23802,7 +25250,10 @@
         <v>1886</v>
       </c>
     </row>
-    <row r="512" spans="4:11">
+    <row r="512" spans="3:11">
+      <c r="C512">
+        <v>1</v>
+      </c>
       <c r="D512" t="s">
         <v>1508</v>
       </c>
@@ -23829,6 +25280,9 @@
       </c>
     </row>
     <row r="513" spans="2:11">
+      <c r="C513">
+        <v>1</v>
+      </c>
       <c r="D513" t="s">
         <v>1508</v>
       </c>
@@ -23858,6 +25312,9 @@
       <c r="B514">
         <v>1</v>
       </c>
+      <c r="C514">
+        <v>1</v>
+      </c>
       <c r="D514" t="s">
         <v>1508</v>
       </c>
@@ -23887,6 +25344,9 @@
       <c r="B515">
         <v>1</v>
       </c>
+      <c r="C515">
+        <v>1</v>
+      </c>
       <c r="D515" t="s">
         <v>1508</v>
       </c>
@@ -23916,6 +25376,9 @@
       <c r="B516">
         <v>1</v>
       </c>
+      <c r="C516">
+        <v>1</v>
+      </c>
       <c r="D516" t="s">
         <v>1508</v>
       </c>
@@ -23945,6 +25408,9 @@
       <c r="B517">
         <v>1</v>
       </c>
+      <c r="C517">
+        <v>1</v>
+      </c>
       <c r="D517" t="s">
         <v>1508</v>
       </c>
@@ -23974,6 +25440,9 @@
       <c r="B518">
         <v>1</v>
       </c>
+      <c r="C518">
+        <v>1</v>
+      </c>
       <c r="D518" t="s">
         <v>1508</v>
       </c>
@@ -24003,6 +25472,9 @@
       <c r="B519">
         <v>1</v>
       </c>
+      <c r="C519">
+        <v>1</v>
+      </c>
       <c r="D519" t="s">
         <v>1508</v>
       </c>
@@ -24032,6 +25504,9 @@
       <c r="B520">
         <v>1</v>
       </c>
+      <c r="C520">
+        <v>1</v>
+      </c>
       <c r="D520" t="s">
         <v>1508</v>
       </c>
@@ -24061,6 +25536,9 @@
       <c r="B521">
         <v>1</v>
       </c>
+      <c r="C521">
+        <v>1</v>
+      </c>
       <c r="D521" t="s">
         <v>1508</v>
       </c>
@@ -24090,6 +25568,9 @@
       <c r="B522">
         <v>1</v>
       </c>
+      <c r="C522">
+        <v>1</v>
+      </c>
       <c r="D522" t="s">
         <v>1508</v>
       </c>
@@ -24119,6 +25600,9 @@
       <c r="B523">
         <v>1</v>
       </c>
+      <c r="C523">
+        <v>1</v>
+      </c>
       <c r="D523" t="s">
         <v>1508</v>
       </c>
@@ -24148,6 +25632,9 @@
       <c r="B524">
         <v>1</v>
       </c>
+      <c r="C524">
+        <v>1</v>
+      </c>
       <c r="D524" t="s">
         <v>1508</v>
       </c>
@@ -24177,6 +25664,9 @@
       <c r="B525">
         <v>1</v>
       </c>
+      <c r="C525">
+        <v>1</v>
+      </c>
       <c r="D525" t="s">
         <v>1508</v>
       </c>
@@ -24206,6 +25696,9 @@
       <c r="B526">
         <v>1</v>
       </c>
+      <c r="C526">
+        <v>1</v>
+      </c>
       <c r="D526" t="s">
         <v>1508</v>
       </c>
@@ -24235,6 +25728,9 @@
       <c r="B527">
         <v>1</v>
       </c>
+      <c r="C527">
+        <v>1</v>
+      </c>
       <c r="D527" t="s">
         <v>1508</v>
       </c>
@@ -24264,6 +25760,9 @@
       <c r="B528">
         <v>1</v>
       </c>
+      <c r="C528">
+        <v>1</v>
+      </c>
       <c r="D528" t="s">
         <v>1508</v>
       </c>
@@ -24293,6 +25792,9 @@
       <c r="B529">
         <v>1</v>
       </c>
+      <c r="C529">
+        <v>1</v>
+      </c>
       <c r="D529" t="s">
         <v>1508</v>
       </c>
@@ -24322,6 +25824,9 @@
       <c r="B530">
         <v>1</v>
       </c>
+      <c r="C530">
+        <v>1</v>
+      </c>
       <c r="D530" t="s">
         <v>1508</v>
       </c>
@@ -24351,6 +25856,9 @@
       <c r="B531">
         <v>1</v>
       </c>
+      <c r="C531">
+        <v>1</v>
+      </c>
       <c r="D531" t="s">
         <v>1508</v>
       </c>
@@ -24438,6 +25946,9 @@
       <c r="B534">
         <v>1</v>
       </c>
+      <c r="C534">
+        <v>1</v>
+      </c>
       <c r="D534" t="s">
         <v>1508</v>
       </c>
@@ -24467,6 +25978,9 @@
       <c r="B535">
         <v>1</v>
       </c>
+      <c r="C535">
+        <v>1</v>
+      </c>
       <c r="D535" t="s">
         <v>1508</v>
       </c>
@@ -24496,6 +26010,9 @@
       <c r="B536">
         <v>1</v>
       </c>
+      <c r="C536">
+        <v>1</v>
+      </c>
       <c r="D536" t="s">
         <v>1508</v>
       </c>
@@ -24525,6 +26042,9 @@
       <c r="B537">
         <v>1</v>
       </c>
+      <c r="C537">
+        <v>1</v>
+      </c>
       <c r="D537" t="s">
         <v>1508</v>
       </c>
@@ -24554,6 +26074,9 @@
       <c r="B538">
         <v>1</v>
       </c>
+      <c r="C538">
+        <v>1</v>
+      </c>
       <c r="D538" t="s">
         <v>1508</v>
       </c>
@@ -25859,6 +27382,9 @@
       <c r="B583">
         <v>1</v>
       </c>
+      <c r="C583">
+        <v>1</v>
+      </c>
       <c r="D583" t="s">
         <v>1508</v>
       </c>
@@ -25888,6 +27414,9 @@
       <c r="B584">
         <v>1</v>
       </c>
+      <c r="C584">
+        <v>1</v>
+      </c>
       <c r="D584" t="s">
         <v>1508</v>
       </c>
@@ -25917,6 +27446,9 @@
       <c r="B585">
         <v>1</v>
       </c>
+      <c r="C585">
+        <v>1</v>
+      </c>
       <c r="D585" t="s">
         <v>1508</v>
       </c>
@@ -26323,6 +27855,9 @@
       <c r="B599">
         <v>1</v>
       </c>
+      <c r="C599">
+        <v>1</v>
+      </c>
       <c r="D599" t="s">
         <v>1508</v>
       </c>
@@ -26613,6 +28148,9 @@
       <c r="B609">
         <v>1</v>
       </c>
+      <c r="C609">
+        <v>1</v>
+      </c>
       <c r="D609" t="s">
         <v>1508</v>
       </c>
@@ -26903,6 +28441,9 @@
       <c r="B619">
         <v>1</v>
       </c>
+      <c r="C619">
+        <v>1</v>
+      </c>
       <c r="D619" t="s">
         <v>1508</v>
       </c>
@@ -26932,6 +28473,9 @@
       <c r="B620">
         <v>1</v>
       </c>
+      <c r="C620">
+        <v>1</v>
+      </c>
       <c r="D620" t="s">
         <v>1508</v>
       </c>
@@ -26961,6 +28505,9 @@
       <c r="B621">
         <v>1</v>
       </c>
+      <c r="C621">
+        <v>1</v>
+      </c>
       <c r="D621" t="s">
         <v>1508</v>
       </c>
@@ -26990,6 +28537,9 @@
       <c r="B622">
         <v>1</v>
       </c>
+      <c r="C622">
+        <v>1</v>
+      </c>
       <c r="D622" t="s">
         <v>1508</v>
       </c>
@@ -27019,6 +28569,9 @@
       <c r="B623">
         <v>1</v>
       </c>
+      <c r="C623">
+        <v>1</v>
+      </c>
       <c r="D623" t="s">
         <v>1508</v>
       </c>
@@ -27048,6 +28601,9 @@
       <c r="B624">
         <v>1</v>
       </c>
+      <c r="C624">
+        <v>1</v>
+      </c>
       <c r="D624" t="s">
         <v>1508</v>
       </c>
@@ -27077,6 +28633,9 @@
       <c r="B625">
         <v>1</v>
       </c>
+      <c r="C625">
+        <v>1</v>
+      </c>
       <c r="D625" t="s">
         <v>1508</v>
       </c>
@@ -27106,6 +28665,9 @@
       <c r="B626">
         <v>1</v>
       </c>
+      <c r="C626">
+        <v>1</v>
+      </c>
       <c r="D626" t="s">
         <v>1508</v>
       </c>
@@ -27135,6 +28697,9 @@
       <c r="B627">
         <v>1</v>
       </c>
+      <c r="C627">
+        <v>1</v>
+      </c>
       <c r="D627" t="s">
         <v>1508</v>
       </c>
@@ -27367,6 +28932,9 @@
       <c r="B635">
         <v>1</v>
       </c>
+      <c r="C635">
+        <v>1</v>
+      </c>
       <c r="D635" t="s">
         <v>1508</v>
       </c>
@@ -27396,6 +28964,9 @@
       <c r="B636">
         <v>1</v>
       </c>
+      <c r="C636">
+        <v>1</v>
+      </c>
       <c r="D636" t="s">
         <v>1508</v>
       </c>
@@ -27425,6 +28996,9 @@
       <c r="B637">
         <v>1</v>
       </c>
+      <c r="C637">
+        <v>1</v>
+      </c>
       <c r="D637" t="s">
         <v>1508</v>
       </c>
@@ -27454,6 +29028,9 @@
       <c r="B638">
         <v>1</v>
       </c>
+      <c r="C638">
+        <v>1</v>
+      </c>
       <c r="D638" t="s">
         <v>1508</v>
       </c>
@@ -27483,6 +29060,9 @@
       <c r="B639">
         <v>1</v>
       </c>
+      <c r="C639">
+        <v>1</v>
+      </c>
       <c r="D639" t="s">
         <v>1508</v>
       </c>
@@ -27512,6 +29092,9 @@
       <c r="B640">
         <v>1</v>
       </c>
+      <c r="C640">
+        <v>1</v>
+      </c>
       <c r="D640" t="s">
         <v>1508</v>
       </c>
@@ -27541,6 +29124,9 @@
       <c r="B641">
         <v>1</v>
       </c>
+      <c r="C641">
+        <v>1</v>
+      </c>
       <c r="D641" t="s">
         <v>1508</v>
       </c>
@@ -27570,6 +29156,9 @@
       <c r="B642">
         <v>1</v>
       </c>
+      <c r="C642">
+        <v>1</v>
+      </c>
       <c r="D642" t="s">
         <v>1508</v>
       </c>
@@ -27683,9 +29272,6 @@
       </c>
     </row>
     <row r="646" spans="1:11">
-      <c r="A646">
-        <v>1</v>
-      </c>
       <c r="B646">
         <v>1</v>
       </c>
@@ -27715,9 +29301,6 @@
       </c>
     </row>
     <row r="647" spans="1:11">
-      <c r="A647">
-        <v>1</v>
-      </c>
       <c r="B647">
         <v>1</v>
       </c>
@@ -27753,9 +29336,6 @@
       <c r="B648">
         <v>1</v>
       </c>
-      <c r="C648">
-        <v>1</v>
-      </c>
       <c r="D648" t="s">
         <v>1508</v>
       </c>
@@ -27795,7 +29375,7 @@
         <v>2447</v>
       </c>
       <c r="F649" t="s">
-        <v>2448</v>
+        <v>2458</v>
       </c>
       <c r="G649" t="s">
         <v>2464</v>
@@ -27807,13 +29387,16 @@
         <v>2466</v>
       </c>
       <c r="J649" t="s">
-        <v>2452</v>
+        <v>2462</v>
       </c>
       <c r="K649" t="s">
         <v>2467</v>
       </c>
     </row>
     <row r="650" spans="1:11">
+      <c r="A650">
+        <v>1</v>
+      </c>
       <c r="B650">
         <v>1</v>
       </c>
@@ -27824,25 +29407,28 @@
         <v>2447</v>
       </c>
       <c r="F650" t="s">
+        <v>2458</v>
+      </c>
+      <c r="G650" t="s">
         <v>2468</v>
       </c>
-      <c r="G650" t="s">
+      <c r="H650" t="s">
         <v>2469</v>
       </c>
-      <c r="H650" t="s">
+      <c r="I650" t="s">
         <v>2470</v>
       </c>
-      <c r="I650" t="s">
+      <c r="J650" t="s">
+        <v>2462</v>
+      </c>
+      <c r="K650" t="s">
         <v>2471</v>
       </c>
-      <c r="J650" t="s">
-        <v>2472</v>
-      </c>
-      <c r="K650" t="s">
-        <v>2473</v>
-      </c>
     </row>
     <row r="651" spans="1:11">
+      <c r="A651">
+        <v>1</v>
+      </c>
       <c r="B651">
         <v>1</v>
       </c>
@@ -27853,25 +29439,28 @@
         <v>2447</v>
       </c>
       <c r="F651" t="s">
+        <v>2458</v>
+      </c>
+      <c r="G651" t="s">
+        <v>2472</v>
+      </c>
+      <c r="H651" t="s">
+        <v>2473</v>
+      </c>
+      <c r="I651" t="s">
         <v>2474</v>
       </c>
-      <c r="G651" t="s">
+      <c r="J651" t="s">
+        <v>2462</v>
+      </c>
+      <c r="K651" t="s">
         <v>2475</v>
       </c>
-      <c r="H651" t="s">
-        <v>2476</v>
-      </c>
-      <c r="I651" t="s">
-        <v>2477</v>
-      </c>
-      <c r="J651" t="s">
-        <v>2478</v>
-      </c>
-      <c r="K651" t="s">
-        <v>2479</v>
-      </c>
     </row>
     <row r="652" spans="1:11">
+      <c r="A652">
+        <v>1</v>
+      </c>
       <c r="B652">
         <v>1</v>
       </c>
@@ -27882,25 +29471,28 @@
         <v>2447</v>
       </c>
       <c r="F652" t="s">
-        <v>2474</v>
+        <v>2458</v>
       </c>
       <c r="G652" t="s">
-        <v>2480</v>
+        <v>2476</v>
       </c>
       <c r="H652" t="s">
-        <v>2481</v>
+        <v>2477</v>
       </c>
       <c r="I652" t="s">
-        <v>2482</v>
+        <v>2478</v>
       </c>
       <c r="J652" t="s">
-        <v>2478</v>
+        <v>2462</v>
       </c>
       <c r="K652" t="s">
-        <v>2483</v>
+        <v>2479</v>
       </c>
     </row>
     <row r="653" spans="1:11">
+      <c r="A653">
+        <v>1</v>
+      </c>
       <c r="B653">
         <v>1</v>
       </c>
@@ -27908,28 +29500,31 @@
         <v>1508</v>
       </c>
       <c r="E653" t="s">
-        <v>2484</v>
+        <v>2447</v>
       </c>
       <c r="F653" t="s">
-        <v>2484</v>
+        <v>2458</v>
       </c>
       <c r="G653" t="s">
-        <v>2485</v>
+        <v>2480</v>
       </c>
       <c r="H653" t="s">
-        <v>2486</v>
+        <v>2481</v>
       </c>
       <c r="I653" t="s">
-        <v>2487</v>
+        <v>2482</v>
       </c>
       <c r="J653" t="s">
-        <v>2488</v>
+        <v>2462</v>
       </c>
       <c r="K653" t="s">
-        <v>2489</v>
+        <v>2483</v>
       </c>
     </row>
     <row r="654" spans="1:11">
+      <c r="A654">
+        <v>1</v>
+      </c>
       <c r="B654">
         <v>1</v>
       </c>
@@ -27937,28 +29532,31 @@
         <v>1508</v>
       </c>
       <c r="E654" t="s">
+        <v>2447</v>
+      </c>
+      <c r="F654" t="s">
+        <v>2458</v>
+      </c>
+      <c r="G654" t="s">
         <v>2484</v>
       </c>
-      <c r="F654" t="s">
-        <v>2484</v>
-      </c>
-      <c r="G654" t="s">
-        <v>2490</v>
-      </c>
       <c r="H654" t="s">
-        <v>2491</v>
+        <v>2485</v>
       </c>
       <c r="I654" t="s">
-        <v>2492</v>
+        <v>2486</v>
       </c>
       <c r="J654" t="s">
-        <v>2488</v>
+        <v>2462</v>
       </c>
       <c r="K654" t="s">
-        <v>2493</v>
+        <v>2487</v>
       </c>
     </row>
     <row r="655" spans="1:11">
+      <c r="A655">
+        <v>1</v>
+      </c>
       <c r="B655">
         <v>1</v>
       </c>
@@ -27966,28 +29564,31 @@
         <v>1508</v>
       </c>
       <c r="E655" t="s">
-        <v>2484</v>
+        <v>2447</v>
       </c>
       <c r="F655" t="s">
-        <v>2484</v>
+        <v>2458</v>
       </c>
       <c r="G655" t="s">
-        <v>2494</v>
+        <v>2488</v>
       </c>
       <c r="H655" t="s">
-        <v>2495</v>
+        <v>2489</v>
       </c>
       <c r="I655" t="s">
-        <v>2496</v>
+        <v>2490</v>
       </c>
       <c r="J655" t="s">
-        <v>2488</v>
+        <v>2462</v>
       </c>
       <c r="K655" t="s">
-        <v>2497</v>
+        <v>2491</v>
       </c>
     </row>
     <row r="656" spans="1:11">
+      <c r="A656">
+        <v>1</v>
+      </c>
       <c r="B656">
         <v>1</v>
       </c>
@@ -27995,28 +29596,31 @@
         <v>1508</v>
       </c>
       <c r="E656" t="s">
-        <v>2484</v>
+        <v>2447</v>
       </c>
       <c r="F656" t="s">
-        <v>2484</v>
+        <v>2458</v>
       </c>
       <c r="G656" t="s">
-        <v>2498</v>
+        <v>2492</v>
       </c>
       <c r="H656" t="s">
-        <v>2499</v>
+        <v>2493</v>
       </c>
       <c r="I656" t="s">
-        <v>2500</v>
+        <v>2494</v>
       </c>
       <c r="J656" t="s">
-        <v>2488</v>
+        <v>2462</v>
       </c>
       <c r="K656" t="s">
-        <v>2501</v>
-      </c>
-    </row>
-    <row r="657" spans="2:11">
+        <v>2495</v>
+      </c>
+    </row>
+    <row r="657" spans="1:11">
+      <c r="A657">
+        <v>1</v>
+      </c>
       <c r="B657">
         <v>1</v>
       </c>
@@ -28024,28 +29628,31 @@
         <v>1508</v>
       </c>
       <c r="E657" t="s">
-        <v>2484</v>
+        <v>2447</v>
       </c>
       <c r="F657" t="s">
-        <v>2484</v>
+        <v>2458</v>
       </c>
       <c r="G657" t="s">
-        <v>2502</v>
+        <v>2496</v>
       </c>
       <c r="H657" t="s">
-        <v>2503</v>
+        <v>2497</v>
       </c>
       <c r="I657" t="s">
-        <v>2504</v>
+        <v>2498</v>
       </c>
       <c r="J657" t="s">
-        <v>2488</v>
+        <v>2462</v>
       </c>
       <c r="K657" t="s">
-        <v>2505</v>
-      </c>
-    </row>
-    <row r="658" spans="2:11">
+        <v>2499</v>
+      </c>
+    </row>
+    <row r="658" spans="1:11">
+      <c r="A658">
+        <v>1</v>
+      </c>
       <c r="B658">
         <v>1</v>
       </c>
@@ -28053,29 +29660,418 @@
         <v>1508</v>
       </c>
       <c r="E658" t="s">
-        <v>744</v>
+        <v>2447</v>
       </c>
       <c r="F658" t="s">
+        <v>2458</v>
+      </c>
+      <c r="G658" t="s">
+        <v>2500</v>
+      </c>
+      <c r="H658" t="s">
+        <v>2501</v>
+      </c>
+      <c r="I658" t="s">
+        <v>2502</v>
+      </c>
+      <c r="J658" t="s">
+        <v>2462</v>
+      </c>
+      <c r="K658" t="s">
+        <v>2503</v>
+      </c>
+    </row>
+    <row r="659" spans="1:11">
+      <c r="A659">
+        <v>1</v>
+      </c>
+      <c r="B659">
+        <v>1</v>
+      </c>
+      <c r="D659" t="s">
+        <v>1508</v>
+      </c>
+      <c r="E659" t="s">
+        <v>2447</v>
+      </c>
+      <c r="F659" t="s">
+        <v>2458</v>
+      </c>
+      <c r="G659" t="s">
+        <v>2504</v>
+      </c>
+      <c r="H659" t="s">
+        <v>2505</v>
+      </c>
+      <c r="I659" t="s">
+        <v>2506</v>
+      </c>
+      <c r="J659" t="s">
+        <v>2462</v>
+      </c>
+      <c r="K659" t="s">
+        <v>2507</v>
+      </c>
+    </row>
+    <row r="660" spans="1:11">
+      <c r="A660">
+        <v>1</v>
+      </c>
+      <c r="B660">
+        <v>1</v>
+      </c>
+      <c r="D660" t="s">
+        <v>1508</v>
+      </c>
+      <c r="E660" t="s">
+        <v>2447</v>
+      </c>
+      <c r="F660" t="s">
+        <v>2458</v>
+      </c>
+      <c r="G660" t="s">
+        <v>2508</v>
+      </c>
+      <c r="H660" t="s">
+        <v>2509</v>
+      </c>
+      <c r="I660" t="s">
+        <v>2510</v>
+      </c>
+      <c r="J660" t="s">
+        <v>2462</v>
+      </c>
+      <c r="K660" t="s">
+        <v>2511</v>
+      </c>
+    </row>
+    <row r="661" spans="1:11">
+      <c r="A661">
+        <v>1</v>
+      </c>
+      <c r="B661">
+        <v>1</v>
+      </c>
+      <c r="D661" t="s">
+        <v>1508</v>
+      </c>
+      <c r="E661" t="s">
+        <v>2447</v>
+      </c>
+      <c r="F661" t="s">
+        <v>2458</v>
+      </c>
+      <c r="G661" t="s">
+        <v>2512</v>
+      </c>
+      <c r="H661" t="s">
+        <v>2513</v>
+      </c>
+      <c r="I661" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J661" t="s">
+        <v>2462</v>
+      </c>
+      <c r="K661" t="s">
+        <v>2515</v>
+      </c>
+    </row>
+    <row r="662" spans="1:11">
+      <c r="B662">
+        <v>1</v>
+      </c>
+      <c r="D662" t="s">
+        <v>1508</v>
+      </c>
+      <c r="E662" t="s">
+        <v>2447</v>
+      </c>
+      <c r="F662" t="s">
+        <v>2448</v>
+      </c>
+      <c r="G662" t="s">
+        <v>2516</v>
+      </c>
+      <c r="H662" t="s">
+        <v>2517</v>
+      </c>
+      <c r="I662" t="s">
+        <v>2518</v>
+      </c>
+      <c r="J662" t="s">
+        <v>2452</v>
+      </c>
+      <c r="K662" t="s">
+        <v>2519</v>
+      </c>
+    </row>
+    <row r="663" spans="1:11">
+      <c r="B663">
+        <v>1</v>
+      </c>
+      <c r="D663" t="s">
+        <v>1508</v>
+      </c>
+      <c r="E663" t="s">
+        <v>2447</v>
+      </c>
+      <c r="F663" t="s">
+        <v>2520</v>
+      </c>
+      <c r="G663" t="s">
+        <v>2521</v>
+      </c>
+      <c r="H663" t="s">
+        <v>2522</v>
+      </c>
+      <c r="I663" t="s">
+        <v>2523</v>
+      </c>
+      <c r="J663" t="s">
+        <v>2524</v>
+      </c>
+      <c r="K663" t="s">
+        <v>2525</v>
+      </c>
+    </row>
+    <row r="664" spans="1:11">
+      <c r="B664">
+        <v>1</v>
+      </c>
+      <c r="D664" t="s">
+        <v>1508</v>
+      </c>
+      <c r="E664" t="s">
+        <v>2447</v>
+      </c>
+      <c r="F664" t="s">
+        <v>2526</v>
+      </c>
+      <c r="G664" t="s">
+        <v>2527</v>
+      </c>
+      <c r="H664" t="s">
+        <v>2528</v>
+      </c>
+      <c r="I664" t="s">
+        <v>2529</v>
+      </c>
+      <c r="J664" t="s">
+        <v>2530</v>
+      </c>
+      <c r="K664" t="s">
+        <v>2531</v>
+      </c>
+    </row>
+    <row r="665" spans="1:11">
+      <c r="B665">
+        <v>1</v>
+      </c>
+      <c r="D665" t="s">
+        <v>1508</v>
+      </c>
+      <c r="E665" t="s">
+        <v>2447</v>
+      </c>
+      <c r="F665" t="s">
+        <v>2526</v>
+      </c>
+      <c r="G665" t="s">
+        <v>2532</v>
+      </c>
+      <c r="H665" t="s">
+        <v>2533</v>
+      </c>
+      <c r="I665" t="s">
+        <v>2534</v>
+      </c>
+      <c r="J665" t="s">
+        <v>2530</v>
+      </c>
+      <c r="K665" t="s">
+        <v>2535</v>
+      </c>
+    </row>
+    <row r="666" spans="1:11">
+      <c r="B666">
+        <v>1</v>
+      </c>
+      <c r="D666" t="s">
+        <v>1508</v>
+      </c>
+      <c r="E666" t="s">
+        <v>2536</v>
+      </c>
+      <c r="F666" t="s">
+        <v>2536</v>
+      </c>
+      <c r="G666" t="s">
+        <v>2537</v>
+      </c>
+      <c r="H666" t="s">
+        <v>2538</v>
+      </c>
+      <c r="I666" t="s">
+        <v>2539</v>
+      </c>
+      <c r="J666" t="s">
+        <v>2540</v>
+      </c>
+      <c r="K666" t="s">
+        <v>2541</v>
+      </c>
+    </row>
+    <row r="667" spans="1:11">
+      <c r="B667">
+        <v>1</v>
+      </c>
+      <c r="D667" t="s">
+        <v>1508</v>
+      </c>
+      <c r="E667" t="s">
+        <v>2536</v>
+      </c>
+      <c r="F667" t="s">
+        <v>2536</v>
+      </c>
+      <c r="G667" t="s">
+        <v>2542</v>
+      </c>
+      <c r="H667" t="s">
+        <v>2543</v>
+      </c>
+      <c r="I667" t="s">
+        <v>2544</v>
+      </c>
+      <c r="J667" t="s">
+        <v>2540</v>
+      </c>
+      <c r="K667" t="s">
+        <v>2545</v>
+      </c>
+    </row>
+    <row r="668" spans="1:11">
+      <c r="B668">
+        <v>1</v>
+      </c>
+      <c r="D668" t="s">
+        <v>1508</v>
+      </c>
+      <c r="E668" t="s">
+        <v>2536</v>
+      </c>
+      <c r="F668" t="s">
+        <v>2536</v>
+      </c>
+      <c r="G668" t="s">
+        <v>2546</v>
+      </c>
+      <c r="H668" t="s">
+        <v>2547</v>
+      </c>
+      <c r="I668" t="s">
+        <v>2548</v>
+      </c>
+      <c r="J668" t="s">
+        <v>2540</v>
+      </c>
+      <c r="K668" t="s">
+        <v>2549</v>
+      </c>
+    </row>
+    <row r="669" spans="1:11">
+      <c r="B669">
+        <v>1</v>
+      </c>
+      <c r="D669" t="s">
+        <v>1508</v>
+      </c>
+      <c r="E669" t="s">
+        <v>2536</v>
+      </c>
+      <c r="F669" t="s">
+        <v>2536</v>
+      </c>
+      <c r="G669" t="s">
+        <v>2550</v>
+      </c>
+      <c r="H669" t="s">
+        <v>2551</v>
+      </c>
+      <c r="I669" t="s">
+        <v>2552</v>
+      </c>
+      <c r="J669" t="s">
+        <v>2540</v>
+      </c>
+      <c r="K669" t="s">
+        <v>2553</v>
+      </c>
+    </row>
+    <row r="670" spans="1:11">
+      <c r="B670">
+        <v>1</v>
+      </c>
+      <c r="D670" t="s">
+        <v>1508</v>
+      </c>
+      <c r="E670" t="s">
+        <v>2536</v>
+      </c>
+      <c r="F670" t="s">
+        <v>2536</v>
+      </c>
+      <c r="G670" t="s">
+        <v>2554</v>
+      </c>
+      <c r="H670" t="s">
+        <v>2555</v>
+      </c>
+      <c r="I670" t="s">
+        <v>2556</v>
+      </c>
+      <c r="J670" t="s">
+        <v>2540</v>
+      </c>
+      <c r="K670" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="671" spans="1:11">
+      <c r="B671">
+        <v>1</v>
+      </c>
+      <c r="C671">
+        <v>1</v>
+      </c>
+      <c r="D671" t="s">
+        <v>1508</v>
+      </c>
+      <c r="E671" t="s">
+        <v>744</v>
+      </c>
+      <c r="F671" t="s">
         <v>1170</v>
       </c>
-      <c r="G658" t="s">
-        <v>2506</v>
-      </c>
-      <c r="H658" t="s">
-        <v>2507</v>
-      </c>
-      <c r="I658" t="s">
-        <v>2508</v>
-      </c>
-      <c r="J658" t="s">
+      <c r="G671" t="s">
+        <v>2558</v>
+      </c>
+      <c r="H671" t="s">
+        <v>2559</v>
+      </c>
+      <c r="I671" t="s">
+        <v>2560</v>
+      </c>
+      <c r="J671" t="s">
         <v>1174</v>
       </c>
-      <c r="K658" t="s">
-        <v>2509</v>
+      <c r="K671" t="s">
+        <v>2561</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L658" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L671" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
